--- a/NEW Product List/New Porduct List.xlsx
+++ b/NEW Product List/New Porduct List.xlsx
@@ -2,20 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WebsiteWithAdmin\NEW Product List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B0AE1C8-784F-49E6-BBCE-00C3BEF2174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F78539-D5F4-434A-AD86-952AB2DB7EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5BB806F1-F28B-4A7F-9AD8-CFC92CC998EC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$T$122</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="20" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="261">
   <si>
     <t>id</t>
   </si>
@@ -632,9 +639,6 @@
     <t>Carbs: , Fiber: , Sodium: , Sugars: , Protein: , Calories: , Total_fat: , Saturated_fat: , Total_servings: 20</t>
   </si>
   <si>
-    <t>5 pcs</t>
-  </si>
-  <si>
     <t>68b1f314-d303-4429-bb42-d4c7cbbd9bec</t>
   </si>
   <si>
@@ -810,6 +814,21 @@
   </si>
   <si>
     <t>Soft Rotis. Pure Home Taste!</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Sum of variant_mrp</t>
+  </si>
+  <si>
+    <t>ready-to-use</t>
   </si>
 </sst>
 </file>
@@ -867,15 +886,332 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -886,6 +1222,3111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="SHIVA" refreshedDate="46212.469922800927" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="121" xr:uid="{422DBEE9-329E-4957-87BF-EB00820EB03A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:T122" sheet="Sheet2"/>
+  </cacheSource>
+  <cacheFields count="20">
+    <cacheField name="id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="command" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="product_name" numFmtId="0">
+      <sharedItems count="29">
+        <s v="Avisaginjala Kaaram"/>
+        <s v="Chinthaku Podi"/>
+        <s v="Dosa Kaaram"/>
+        <s v="Kadapa Kaaram"/>
+        <s v="Kandi Podi"/>
+        <s v="Karivepaku Podi"/>
+        <s v="Karnataka Idli Podi"/>
+        <s v="Konaseema Kaaram"/>
+        <s v="Koora Kaaram"/>
+        <s v="Kothimera Kaaram"/>
+        <s v="Moringa Kaaram"/>
+        <s v="Nalla Kaaram"/>
+        <s v="Palli Kaaram"/>
+        <s v="Pudina Kaaram"/>
+        <s v="Putnala Podi"/>
+        <s v="Special Godhuma Kaaram"/>
+        <s v="Special Palli Kaaram"/>
+        <s v="Tamalapaaku Kaaram"/>
+        <s v="Velluli Kaaram"/>
+        <s v="Chutney Premix"/>
+        <s v="MultiGrain Mix"/>
+        <s v="Sambar Premix"/>
+        <s v="Peri Peri Masala"/>
+        <s v="Ragi Chapati"/>
+        <s v="Malabar Parota (10pcs)"/>
+        <s v="Whole Wheat Parota"/>
+        <s v="Poori"/>
+        <s v="Wheat Chapathi"/>
+        <s v="Malabar Parota (5pcs)"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="product_name_telugu" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="product_category" numFmtId="0">
+      <sharedItems count="3">
+        <s v="ready-to-eat"/>
+        <s v="ready-to-use"/>
+        <s v="ready-to-cook"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="product_tagline" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="product_description" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="ingredients" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="serving_suggestion" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="serving_size" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="40"/>
+    </cacheField>
+    <cacheField name="nutrition" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="is_trending" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="is_visible" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="shelf_life" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="30" maxValue="120"/>
+    </cacheField>
+    <cacheField name="is_refrigerated" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="variant_qty" numFmtId="0">
+      <sharedItems count="7">
+        <s v="100g"/>
+        <s v="250g"/>
+        <s v="500g"/>
+        <s v="1000g"/>
+        <s v="10pcs"/>
+        <s v="5pcs"/>
+        <s v="5 pcs" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="variant_mrp" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="810"/>
+    </cacheField>
+    <cacheField name="variant_price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="810"/>
+    </cacheField>
+    <cacheField name="variant_stock" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="96" maxValue="996"/>
+    </cacheField>
+    <cacheField name="variant_packaging" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Standup Pouch"/>
+        <s v="Pouch"/>
+        <s v="Glass Jar"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="121">
+  <r>
+    <s v="d40333db-fc45-4a73-9329-eb54ef6a85b5"/>
+    <m/>
+    <x v="0"/>
+    <s v="అవిసగింజల కారం"/>
+    <x v="0"/>
+    <s v="Healthy Bite, Enriched with Ragi!"/>
+    <s v="A wholesome podi enriched with flax seeds and finger millet (ragi). Nutty, spicy, and lightly sweet, it delivers nutrition and taste in every bite."/>
+    <s v="Flax Seed, Urad Dal, Peanuts, Finger Millet, Dry Red Chilly, Salt, Garlic, Cloves, Tamarind, Jaggery, Cardamom, Curry Leaf, Cinnamon"/>
+    <s v="Add the desired amount of podi to hot rice. Mix in a spoonful of ghee to enhance the flavor and aroma. Serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.84kcal, Protein 0.85g, Total Fat 1.13g, Saturated Fat 0.14g, Carbs 2.03g, Fiber 1.1g, Sugars 0.21g, Sodium 0.1g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="55"/>
+    <n v="55"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="a72fb41d-834f-4e95-8207-933ee4ce2a47"/>
+    <m/>
+    <x v="1"/>
+    <s v="చింతాకు పొడి"/>
+    <x v="0"/>
+    <s v="Tangy. Nutty. Traditionally Bold!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Peanuts, Black Sesame Seeds, Tamarind Leaves, Dry Red Chilly, Garlic, Coriander, Salt"/>
+    <s v="Add this tangy blend of chinthaku, roasted peanuts, and black sesame to hot rice. Mix in a good serving of ghee and serve warm."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 24.99kcal, Protein 0.96g, Total Fat 1.86g, Saturated Fat 0.3g, Carbs 1.46g, Fiber 0.61g, Sugars 0.13g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="70"/>
+    <n v="70"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="5fd5ad76-ce6b-4a27-b189-bd32180f3c7c"/>
+    <m/>
+    <x v="2"/>
+    <s v="దోశ కారం"/>
+    <x v="0"/>
+    <s v="Perfect Spice for Crispy Dosas!"/>
+    <s v="A flavorful podi crafted for crispy dosas. Made with poha, lentils, and aromatic spices, it adds a nutty, spicy kick that enhances every bite with ghee."/>
+    <s v="Poha, Chickpea, Urad Dal, Coriander, Red Chilly Powder, Dry Red Chilly, Salt, Cumin, Curry Leaf, Garlic, Marathi Moggu, Cinnamon"/>
+    <s v="Evenly dust this vibrant mix of [Ingredient 1] and spices onto your roasting dosa. Finish with a touch of ghee for a spicy, flavorful bite."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.16kcal, Protein 0.67g, Total Fat 0.2g, Saturated Fat 0.02g, Carbs 3.13g, Fiber 0.83g, Sugars 0.17g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="031d0c4a-11ea-49ab-aae9-b7b7d05bd29e"/>
+    <m/>
+    <x v="3"/>
+    <s v="కడప కారం"/>
+    <x v="0"/>
+    <s v="Bold flavor, rich and hearty!"/>
+    <s v="A signature Andhra blend that balances peanuts, garlic, and dry coconut with a fiery kick of red chili. Rich, hearty, and versatile — a true taste of Kadapa tradition."/>
+    <s v="Peanuts, Garlic, Dry Coconut, Cumin, Dry Red Chilly, Coriander, Jaggery, Salt, Red Chilly Powder, Curry Leaf, Lemon Salt"/>
+    <s v="Sprinkle this versatile, sweet-and-spicy blend of peanuts, garlic, and dry coconut over dosas, or mix it into hot rice with ghee. "/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.88kcal, Protein 0.7g, Total Fat 1.49g, Saturated Fat 0.75g, Carbs 1.51g, Fiber 0.64g, Sugars 0.31g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="NEW"/>
+    <s v="ADD"/>
+    <x v="4"/>
+    <s v="కంది పొడి"/>
+    <x v="0"/>
+    <s v="Roasted Lentils,.Pure Comfort!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Red Gram, Chickpea, Dry Red Chilly, Coriander, Urad Dal, Garlic, Cumin, Curry Leaf, White Sesame Seeds, Salt, Mung Bean, Fresh Coriander, Red Chilly Powder, Asafoetida"/>
+    <s v="Enjoy the traditional flavor of this multipurpose blend of roasted dals, garlic, and a hint of hing. Mix it into hot rice with a spoonful of ghee, or pair it with your daily tiffins!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.02kcal, Protein 0.92g, Total Fat 0.29g, Saturated Fat 0.04g, Carbs 2.71g, Fiber 0.92g, Sugars 0.12g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="55"/>
+    <n v="55"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="d4eb273f-08a8-4f6b-bfac-8c4dce9c5511"/>
+    <m/>
+    <x v="5"/>
+    <s v="కరివేపాకు పొడి"/>
+    <x v="0"/>
+    <s v="Earthy.Spicy. Naturally Good!"/>
+    <s v="A must-try Andhra specialty made with fragrant curry leaves, dals, and spices. Earthy and wholesome, this podi pairs beautifully with hot rice and ghee for a nourishing meal."/>
+    <s v="Curry Leaf, Garlic, Urad Dal, Dry Red Chilly, Chickpea, Coriander, Tamarind, Salt, Cumin, Fenugreek"/>
+    <s v="Mix the desired amount of this earthy curry leaf, garlic, and tamarind blend into hot rice. Stir in a generous serving of ghee for a comforting, traditional meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.71kcal, Protein 0.81g, Total Fat 0.2g, Saturated Fat 0.05g, Carbs 2.39g, Fiber 1.33g, Sugars 0.23g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="38b67b7f-2441-4024-88f1-f3f0c0a29d00"/>
+    <m/>
+    <x v="6"/>
+    <s v="కర్ణాటక ఇడ్లీ పొడి"/>
+    <x v="0"/>
+    <s v="Idli’s Best Friends: Ghee &amp; Podi!"/>
+    <s v="A classic South Indian podi made with chickpeas, urad dal, and spices. Perfectly balanced for hot idlis with ghee, adding a nutty, mildly spicy flavor every time."/>
+    <s v="Chickpea, Urad Dal, Dry Red Chilly, Salt, Cumin, Black Pepper, Red Chilly Powder, Curry Leaf"/>
+    <s v="Mix this classic blend of roasted dals and black pepper with a generous spoonful of ghee. Spread it right on top for a perfect bite!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.22kcal, Protein 1.03g, Total Fat 0.16g, Saturated Fat 0.02g, Carbs 2.91g, Fiber 1.02g, Sugars 0.32g, Sodium 0.08g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="50"/>
+    <n v="50"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="05dd8c31-48da-4ea0-84bd-345c7c25b5f9"/>
+    <m/>
+    <x v="7"/>
+    <s v="కోనసీమ కారం"/>
+    <x v="0"/>
+    <s v="Superfoods Meet Fiery Tradition!"/>
+    <s v="A signature spice blend inspired by the coastal Konaseema region. Blends dry coconut, garlic, and red chilies for a rich, aromatic flavor."/>
+    <s v="Curry Leaf, Flax Seed, Peanuts, Moringa, Dry Red Chilly, Chickpea, Coriander, Raisin, Fresh Mint, Tamarind, Urad Dal, White Sesame Seeds, Salt, Ginger, Asafoetida"/>
+    <s v="Place Holder"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 15.47kcal, Protein 0.81g, Total Fat 0.71g, Saturated Fat 0.11g, Carbs 1.88g, Fiber 1.1g, Sugars 0.35g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="30"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="75"/>
+    <n v="75"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="7421e0f3-7316-47eb-b75c-c5d92763b9fd"/>
+    <m/>
+    <x v="8"/>
+    <s v="కూర కారం"/>
+    <x v="0"/>
+    <s v="Sauté. Sprinkle. Savor Garlic!"/>
+    <s v="The essential Telugu multi-purpose spice mix used for seasoning daily curries, fries, and gravies. Perfect balance of spices."/>
+    <s v="Dry Coconut, Garlic, Red Chilly Powder, Coriander, Salt"/>
+    <s v="Sauté your everyday vegetables, sprinkle this rich blend of garlic and dry coconut over the top, and savor the bold flavor!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.76kcal, Protein 0.39g, Total Fat 1.64g, Saturated Fat 1.37g, Carbs 1.55g, Fiber 0.95g, Sugars 0.23g, Sodium 0.2g"/>
+    <b v="0"/>
+    <b v="0"/>
+    <n v="45"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="98df3516-f8f6-4379-b45e-513b78971171"/>
+    <m/>
+    <x v="9"/>
+    <s v="కొత్తిమీర కారం"/>
+    <x v="0"/>
+    <s v="Zesty coriander Spark – Freshness in Every Spoon!"/>
+    <s v="A vibrant, aromatic spice powder made with fresh sun-dried coriander leaves, roasted dals, and garlic. Earthy and fresh."/>
+    <s v="Red Chilly Powder, Fresh Coriander, Red Gram, Urad Dal, Salt, Poha, Dry Red Chilly, Cumin, Jaggery, Tamarind"/>
+    <s v="Toss this flavorful mix of coriander and roasted dals with hot rice and ghee to bring out the rich, herby aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.34kcal, Protein 0.54g, Total Fat 0.23g, Saturated Fat 0.04g, Carbs 2.37g, Fiber 0.77g, Sugars 0.48g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="581f07ae-4d33-4fa1-8915-655e48c183c3"/>
+    <m/>
+    <x v="10"/>
+    <s v="మునగాకు కారం"/>
+    <x v="0"/>
+    <s v="Moringa Magic: Nutritious. Natural. Delicious!"/>
+    <s v="A nutrient-dense South Indian spice blend combining superfood Moringa leaves with roasted lentils and seeds for a savory, earthy flavor. This all-natural &quot;miracle podi&quot; delivers a potent boost of vitamins and antioxidants in every spoonful."/>
+    <s v="Red Gram, Moringa, Chickpea, Pumpkin Seeds, Salt, Dry Red Chilly, Cumin, Black Pepper, Curry Leaf, Mint Leaves, Lemon Salt"/>
+    <s v="Mix the desired amount of this moringa, pumpkin seed blend into hot rice. Stir in a generous serving of ghee for a nutritious meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.43kcal, Protein 0.85g, Total Fat 0.39g, Saturated Fat 0.06g, Carbs 1.85g, Fiber 0.62g, Sugars 0.09g, Sodium 0.22g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="65"/>
+    <n v="65"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ba2fe49f-75f1-4db0-b2d0-edd26d81cc62"/>
+    <m/>
+    <x v="11"/>
+    <s v="నల్ల కారం"/>
+    <x v="0"/>
+    <s v="High fiber, gut-friendly spice!"/>
+    <s v="A wholesome Andhra classic made with tamarind, dals, and garlic. High in fiber and flavor, this podi adds a tangy, spicy twist to everyday favorites."/>
+    <s v="Dry Red Chilly, Chickpea, Urad Dal, Tamarind, Garlic, Coriander, Cumin, Salt, Ghee, Ginger, Jaggery, Curry Leaf"/>
+    <s v="Enjoy this hotel-style blend of roasted dals, fiery chilies, and garlic. Mix it with ghee to dip soft idlis, or sprinkle it over a roasting dosa!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 14.95kcal, Protein 0.63g, Total Fat 0.47g, Saturated Fat 0.15g, Carbs 2.47g, Fiber 0.91g, Sugars 0.52g, Sodium 0.11g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="55"/>
+    <n v="55"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="285b7b12-59d1-47a0-afb2-986c6c72d045"/>
+    <m/>
+    <x v="12"/>
+    <s v="పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Palli Kaaram. Boldly Telugu!"/>
+    <s v="A nutty and spicy Kadapa classic made with peanuts, chili, and curry leaves. A true part of local culture — delicious with rice or even as a snack on its own."/>
+    <s v="Peanuts, Curry Leaf, Dry Red Chilly, Garlic, Red Chilly Powder, Salt, Cumin"/>
+    <s v="Add this unique Rayalaseema blend of roasted peanuts, garlic, and curry leaves to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 25.87kcal, Protein 1.24g, Total Fat 2.04g, Saturated Fat 0.36g, Carbs 1.02g, Fiber 0.64g, Sugars 0.2g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="55"/>
+    <n v="55"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="3d01988a-ad7d-4114-908b-38098cd63bd3"/>
+    <m/>
+    <x v="13"/>
+    <s v="పుదిన కారం"/>
+    <x v="0"/>
+    <s v="Light, Lively &amp; Minty-Perfect!"/>
+    <s v="A refreshing and aromatic South Indian spice blend featuring sun-dried mint, garlic, and roasted lentils for a zesty, herbaceous kick. This flavorful podi acts as a natural palate cleanser while providing a cooling, gut-friendly boost to your daily meals."/>
+    <s v="Red Chilly Powder, Mint Leaves, Urad Dal, Red Gram, Poha, Salt, Dry Red Chilly, Cumin, Tamarind, Jaggery"/>
+    <s v="Add this refreshing blend of mint leaves, roasted dals, and a hint of tamarind to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.89kcal, Protein 0.65g, Total Fat 0.26g, Saturated Fat 0.05g, Carbs 2.65g, Fiber 0.95g, Sugars 0.47g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="5d7272ee-37e6-43c3-bb9d-551dc2d7da38"/>
+    <m/>
+    <x v="14"/>
+    <s v=" పుట్నాల పొడి"/>
+    <x v="0"/>
+    <s v="Flavor-packed, protein-rich!"/>
+    <s v="A protein-rich lentil blend from Kadapa, this podi combines fried gram, coconut, and garlic for a nutty, savory taste. Traditionally enjoyed with pickle rice and ghee for an extra flavor boost."/>
+    <s v="Fried Gram, Dry Coconut, Garlic, Red Chilly Powder, Salt"/>
+    <s v="Add this classic blend of fried gram, dry coconut, and garlic to hot rice. Mix in a spoonful of ghee and pair with your favorite pickle for a perfect meal!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 18kcal, Protein 0.9g, Total Fat 0.55g, Saturated Fat 0.31g, Carbs 2.53g, Fiber 0.6g, Sugars 0.45g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="50"/>
+    <n v="50"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2cf104b5-c88f-48a7-9e5e-741a20cc2c20"/>
+    <m/>
+    <x v="15"/>
+    <s v="స్పెషల్ గోధుమ కారం"/>
+    <x v="0"/>
+    <s v="Tasty, Light &amp; Fresh!"/>
+    <s v="A wholesome, nutty podi made with chakki atta, dals, coconut, and garlic. Perfectly balanced, it brings a bold, hearty flavor to your meals."/>
+    <s v="Chakki Atta, Urad Dal, Red Chilly Powder, Dry Coconut, Flax Seed, Garlic, Salt"/>
+    <s v="Smear this unique, nutty mix of whole wheat, urad dal, and garlic onto dosas, or pair it with melted ghee for the perfect savory idli dip."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.24kcal, Protein 0.68g, Total Fat 0.41g, Saturated Fat 0.2g, Carbs 2.93g, Fiber 0.76g, Sugars 0.09g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="0219fa3e-9afc-4048-aba2-e9daa0fba81e"/>
+    <m/>
+    <x v="16"/>
+    <s v=" స్పెషల్ పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Rustic. Rich. Ridiculously Good!"/>
+    <s v="Our best-reviewed podi! A rustic blend of peanuts, coriander, and jaggery that delivers mellow, nutty flavors. Smooth and balanced, it’s even loved by kids when mixed with hot rice and ghee."/>
+    <s v="Peanuts, Fried Gram, Coriander, Jaggery, Dry Red Chilly, Salt, Tamarind"/>
+    <s v="Toss this flavorful mix of peanuts, fried gram, and coriander with hot rice and a good serving of ghee to beautifully bring out the sweet and tangy notes."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 19.99kcal, Protein 0.87g, Total Fat 1.03g, Saturated Fat 0.16g, Carbs 2.23g, Fiber 0.69g, Sugars 0.85g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="976a762d-59d8-421e-8a1a-dc0bd38850ea"/>
+    <m/>
+    <x v="17"/>
+    <s v="తమలపాకు కారం"/>
+    <x v="0"/>
+    <s v="Wellness in Every Bite – Betel Leaf at the Heart!"/>
+    <s v="A unique, health-focused herbal spice powder combining fresh betel leaves (Tamalapaaku) with traditional roasted spices and lentils."/>
+    <s v="Betel Leaf, Garlic, Urad Dal, Chickpea, Peanuts, Red Chilly Powder, Cumin, White Sesame Seeds, Coriander, Salt, Curry Leaf"/>
+    <s v="Stir this vibrantly fresh betel leaf and sesame mix into hot rice with a spoonful of ghee for an uplifting flavor."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.23kcal, Protein 0.66g, Total Fat 0.57g, Saturated Fat 0.09g, Carbs 1.64g, Fiber 0.65g, Sugars 0.16g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="6bb57327-d5c7-4a3f-b645-031fe220a609"/>
+    <m/>
+    <x v="18"/>
+    <s v="వెల్లుల్లి కారం"/>
+    <x v="0"/>
+    <s v="Three Ingredients. Infinite Flavor!"/>
+    <s v="A garlicky podi with dry coconut and spices, a staple in every Kadapa household. Adds delicious flavor to sautéed vegetables or can be used as a base for curries."/>
+    <s v="Garlic, Red Chilly Powder, Salt, Sunflower Oil"/>
+    <s v="Smear this savory garlic blend onto hot dosas, or toss it with hot rice and ghee to bring out the roasted aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 10.59kcal, Protein 0.42g, Total Fat 0.45g, Saturated Fat 0.07g, Carbs 1.77g, Fiber 0.75g, Sugars 0.17g, Sodium 0.25g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="81095baa-0101-4c50-8749-051c376d8fd8"/>
+    <m/>
+    <x v="19"/>
+    <s v="చట్నీ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Fresh Chutney in a Snap!"/>
+    <s v="A quick and easy blend of peanuts, gram, and spices. Just add water and grind to make a smooth, flavorful Palli (groundnut) chutney in minutes."/>
+    <s v="Peanuts, Fried Gram, Dry Red Chilly, Salt, Ginger, Tamarind, Coriander Powder"/>
+    <s v="Simply add water gradually to this flavorful blend until you reach your desired consistency.Ready in seconds to pair with hot tiffin."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 178.61kcal, Protein 9.01g, Total Fat 10.89g, Saturated Fat 1.83g, Carbs 13.74g, Fiber 5.08g, Sugars 2.74g, Sodium 0.64g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="45"/>
+    <n v="45"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="9b6b3df2-7a39-407f-b320-9d6f6e9b0db9"/>
+    <m/>
+    <x v="20"/>
+    <s v="మల్టీ గ్రెయిన్ మిక్స్"/>
+    <x v="1"/>
+    <s v="Power of 13 Grains, Strength in Every Bite!"/>
+    <s v="A wholesome blend of 13 grains and legumes, designed to make multigrain chapatis at home. Nutritious and flavorful, it turns every bite into a healthy delight."/>
+    <s v="Horse Gram, Red Gram, Cornflour, Oats, Finger Millet, Soybean, Pearl Millet, Chickpea, Mung Bean, White Sesame Seeds, Urad Dal, Red Chilly Powder, Garlic, Coriander"/>
+    <s v="Add this mix to chakki atta in 1:5 ratio before making the dough, to get the health benefits of 13 grains in every bite."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 146.89kcal, Protein 7.23g, Total Fat 2.84g, Saturated Fat 0.42g, Carbs 23.55g, Fiber 4.57g, Sugars 0.89g, Sodium 0.04g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="40"/>
+    <n v="40"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="21685c21-498d-43b2-88ea-5a64964d64e8"/>
+    <m/>
+    <x v="21"/>
+    <s v="సాంబార్ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Authentic Sambar in a Snap!"/>
+    <s v="A convenient, ready-to-use blend of rice, lentils, spices, and tamarind. Just add vegetables and boil to enjoy a flavorful, authentic South Indian sambar in minutes."/>
+    <s v="Rice, Dry Red Chilly, Coriander, Red Gram, Urad Dal, Chickpea, Tamarind, Salt, Dry Coconut, Cumin, Fenugreek, Cinnamon, Curry Leaf"/>
+    <s v="Add 40g of this authentic blend to 1 liter of water along with your favorite fresh vegetables. Boil until tender for fresh sambar."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 127.92kcal, Protein 5.03g, Total Fat 3.08g, Saturated Fat 1.3g, Carbs 22.92g, Fiber 7.42g, Sugars 2.16g, Sodium 1.13g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="50"/>
+    <n v="50"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="cc119ff6-8f5b-4913-97a1-fb2a95cb2989"/>
+    <m/>
+    <x v="22"/>
+    <s v="పెరి పెరి మసాలా"/>
+    <x v="1"/>
+    <s v="Fiery, Tangy, Totally Irresistible!"/>
+    <s v="A fiery, zesty fusion blend of African bird's eye chilies, garlic, herbs, and spices. Perfect for fries, chips, and snacks."/>
+    <s v="Sugar, Salt, Red Chilly Powder, Onion Powder, Kashmiri Red Chilly Powder, Garlic Powder, Amchur Powder, Black Pepper, Oregano"/>
+    <s v="Dust this zesty chili and herb mix generously over popcorn, makhana, or roasted nuts for a perfectly spicy snack."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.46kcal, Protein 0.32g, Total Fat 0.14g, Saturated Fat 0.04g, Carbs 3.08g, Fiber 0.6g, Sugars 0.92g, Sodium 0.3g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="80"/>
+    <n v="80"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="d40333db-fc45-4a73-9329-eb54ef6a85b5"/>
+    <m/>
+    <x v="0"/>
+    <s v="అవిసగింజల కారం"/>
+    <x v="0"/>
+    <s v="Healthy Bite, Enriched with Ragi!"/>
+    <s v="A wholesome podi enriched with flax seeds and finger millet (ragi). Nutty, spicy, and lightly sweet, it delivers nutrition and taste in every bite."/>
+    <s v="Flax Seed, Urad Dal, Peanuts, Finger Millet, Dry Red Chilly, Salt, Garlic, Cloves, Tamarind, Jaggery, Cardamom, Curry Leaf, Cinnamon"/>
+    <s v="Add the desired amount of podi to hot rice. Mix in a spoonful of ghee to enhance the flavor and aroma. Serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.84kcal, Protein 0.85g, Total Fat 1.13g, Saturated Fat 0.14g, Carbs 2.03g, Fiber 1.1g, Sugars 0.21g, Sodium 0.1g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="135"/>
+    <n v="135"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="a72fb41d-834f-4e95-8207-933ee4ce2a47"/>
+    <m/>
+    <x v="1"/>
+    <s v="చింతాకు పొడి"/>
+    <x v="0"/>
+    <s v="Tangy. Nutty. Traditionally Bold!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Peanuts, Black Sesame Seeds, Tamarind Leaves, Dry Red Chilly, Garlic, Coriander, Salt"/>
+    <s v="Add this tangy blend of chinthaku, roasted peanuts, and black sesame to hot rice. Mix in a good serving of ghee and serve warm."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 24.99kcal, Protein 0.96g, Total Fat 1.86g, Saturated Fat 0.3g, Carbs 1.46g, Fiber 0.61g, Sugars 0.13g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="170"/>
+    <n v="170"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="5fd5ad76-ce6b-4a27-b189-bd32180f3c7c"/>
+    <m/>
+    <x v="2"/>
+    <s v="దోశ కారం"/>
+    <x v="0"/>
+    <s v="Perfect Spice for Crispy Dosas!"/>
+    <s v="A flavorful podi crafted for crispy dosas. Made with poha, lentils, and aromatic spices, it adds a nutty, spicy kick that enhances every bite with ghee."/>
+    <s v="Poha, Chickpea, Urad Dal, Coriander, Red Chilly Powder, Dry Red Chilly, Salt, Cumin, Curry Leaf, Garlic, Marathi Moggu, Cinnamon"/>
+    <s v="Evenly dust this vibrant mix of [Ingredient 1] and spices onto your roasting dosa. Finish with a touch of ghee for a spicy, flavorful bite."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.16kcal, Protein 0.67g, Total Fat 0.2g, Saturated Fat 0.02g, Carbs 3.13g, Fiber 0.83g, Sugars 0.17g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="031d0c4a-11ea-49ab-aae9-b7b7d05bd29e"/>
+    <m/>
+    <x v="3"/>
+    <s v="కడప కారం"/>
+    <x v="0"/>
+    <s v="Bold flavor, rich and hearty!"/>
+    <s v="A signature Andhra blend that balances peanuts, garlic, and dry coconut with a fiery kick of red chili. Rich, hearty, and versatile — a true taste of Kadapa tradition."/>
+    <s v="Peanuts, Garlic, Dry Coconut, Cumin, Dry Red Chilly, Coriander, Jaggery, Salt, Red Chilly Powder, Curry Leaf, Lemon Salt"/>
+    <s v="Sprinkle this versatile, sweet-and-spicy blend of peanuts, garlic, and dry coconut over dosas, or mix it into hot rice with ghee. "/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.88kcal, Protein 0.7g, Total Fat 1.49g, Saturated Fat 0.75g, Carbs 1.51g, Fiber 0.64g, Sugars 0.31g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="NEW"/>
+    <s v="ADD"/>
+    <x v="4"/>
+    <s v="కంది పొడి"/>
+    <x v="0"/>
+    <s v="Roasted Lentils,.Pure Comfort!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Red Gram, Chickpea, Dry Red Chilly, Coriander, Urad Dal, Garlic, Cumin, Curry Leaf, White Sesame Seeds, Salt, Mung Bean, Fresh Coriander, Red Chilly Powder, Asafoetida"/>
+    <s v="Enjoy the traditional flavor of this multipurpose blend of roasted dals, garlic, and a hint of hing. Mix it into hot rice with a spoonful of ghee, or pair it with your daily tiffins!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.02kcal, Protein 0.92g, Total Fat 0.29g, Saturated Fat 0.04g, Carbs 2.71g, Fiber 0.92g, Sugars 0.12g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="135"/>
+    <n v="135"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="d4eb273f-08a8-4f6b-bfac-8c4dce9c5511"/>
+    <m/>
+    <x v="5"/>
+    <s v="కరివేపాకు పొడి"/>
+    <x v="0"/>
+    <s v="Earthy.Spicy. Naturally Good!"/>
+    <s v="A must-try Andhra specialty made with fragrant curry leaves, dals, and spices. Earthy and wholesome, this podi pairs beautifully with hot rice and ghee for a nourishing meal."/>
+    <s v="Curry Leaf, Garlic, Urad Dal, Dry Red Chilly, Chickpea, Coriander, Tamarind, Salt, Cumin, Fenugreek"/>
+    <s v="Mix the desired amount of this earthy curry leaf, garlic, and tamarind blend into hot rice. Stir in a generous serving of ghee for a comforting, traditional meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.71kcal, Protein 0.81g, Total Fat 0.2g, Saturated Fat 0.05g, Carbs 2.39g, Fiber 1.33g, Sugars 0.23g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="38b67b7f-2441-4024-88f1-f3f0c0a29d00"/>
+    <m/>
+    <x v="6"/>
+    <s v="కర్ణాటక ఇడ్లీ పొడి"/>
+    <x v="0"/>
+    <s v="Idli’s Best Friends: Ghee &amp; Podi!"/>
+    <s v="A classic South Indian podi made with chickpeas, urad dal, and spices. Perfectly balanced for hot idlis with ghee, adding a nutty, mildly spicy flavor every time."/>
+    <s v="Chickpea, Urad Dal, Dry Red Chilly, Salt, Cumin, Black Pepper, Red Chilly Powder, Curry Leaf"/>
+    <s v="Mix this classic blend of roasted dals and black pepper with a generous spoonful of ghee. Spread it right on top for a perfect bite!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.22kcal, Protein 1.03g, Total Fat 0.16g, Saturated Fat 0.02g, Carbs 2.91g, Fiber 1.02g, Sugars 0.32g, Sodium 0.08g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="05dd8c31-48da-4ea0-84bd-345c7c25b5f9"/>
+    <m/>
+    <x v="7"/>
+    <s v="కోనసీమ కారం"/>
+    <x v="0"/>
+    <s v="Superfoods Meet Fiery Tradition!"/>
+    <s v="A signature spice blend inspired by the coastal Konaseema region. Blends dry coconut, garlic, and red chilies for a rich, aromatic flavor."/>
+    <s v="Curry Leaf, Flax Seed, Peanuts, Moringa, Dry Red Chilly, Chickpea, Coriander, Raisin, Fresh Mint, Tamarind, Urad Dal, White Sesame Seeds, Salt, Ginger, Asafoetida"/>
+    <s v="Place Holder"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 15.47kcal, Protein 0.81g, Total Fat 0.71g, Saturated Fat 0.11g, Carbs 1.88g, Fiber 1.1g, Sugars 0.35g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="30"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="180"/>
+    <n v="180"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="7421e0f3-7316-47eb-b75c-c5d92763b9fd"/>
+    <m/>
+    <x v="8"/>
+    <s v="కూర కారం"/>
+    <x v="0"/>
+    <s v="Sauté. Sprinkle. Savor Garlic!"/>
+    <s v="The essential Telugu multi-purpose spice mix used for seasoning daily curries, fries, and gravies. Perfect balance of spices."/>
+    <s v="Dry Coconut, Garlic, Red Chilly Powder, Coriander, Salt"/>
+    <s v="Sauté your everyday vegetables, sprinkle this rich blend of garlic and dry coconut over the top, and savor the bold flavor!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.76kcal, Protein 0.39g, Total Fat 1.64g, Saturated Fat 1.37g, Carbs 1.55g, Fiber 0.95g, Sugars 0.23g, Sodium 0.2g"/>
+    <b v="0"/>
+    <b v="0"/>
+    <n v="45"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="98df3516-f8f6-4379-b45e-513b78971171"/>
+    <m/>
+    <x v="9"/>
+    <s v="కొత్తిమీర కారం"/>
+    <x v="0"/>
+    <s v="Zesty coriander Spark – Freshness in Every Spoon!"/>
+    <s v="A vibrant, aromatic spice powder made with fresh sun-dried coriander leaves, roasted dals, and garlic. Earthy and fresh."/>
+    <s v="Red Chilly Powder, Fresh Coriander, Red Gram, Urad Dal, Salt, Poha, Dry Red Chilly, Cumin, Jaggery, Tamarind"/>
+    <s v="Toss this flavorful mix of coriander and roasted dals with hot rice and ghee to bring out the rich, herby aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.34kcal, Protein 0.54g, Total Fat 0.23g, Saturated Fat 0.04g, Carbs 2.37g, Fiber 0.77g, Sugars 0.48g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="581f07ae-4d33-4fa1-8915-655e48c183c3"/>
+    <m/>
+    <x v="10"/>
+    <s v="మునగాకు కారం"/>
+    <x v="0"/>
+    <s v="Moringa Magic: Nutritious. Natural. Delicious!"/>
+    <s v="A nutrient-dense South Indian spice blend combining superfood Moringa leaves with roasted lentils and seeds for a savory, earthy flavor. This all-natural &quot;miracle podi&quot; delivers a potent boost of vitamins and antioxidants in every spoonful."/>
+    <s v="Red Gram, Moringa, Chickpea, Pumpkin Seeds, Salt, Dry Red Chilly, Cumin, Black Pepper, Curry Leaf, Mint Leaves, Lemon Salt"/>
+    <s v="Mix the desired amount of this moringa, pumpkin seed blend into hot rice. Stir in a generous serving of ghee for a nutritious meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.43kcal, Protein 0.85g, Total Fat 0.39g, Saturated Fat 0.06g, Carbs 1.85g, Fiber 0.62g, Sugars 0.09g, Sodium 0.22g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="160"/>
+    <n v="160"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="ba2fe49f-75f1-4db0-b2d0-edd26d81cc62"/>
+    <m/>
+    <x v="11"/>
+    <s v="నల్ల కారం"/>
+    <x v="0"/>
+    <s v="High fiber, gut-friendly spice!"/>
+    <s v="A wholesome Andhra classic made with tamarind, dals, and garlic. High in fiber and flavor, this podi adds a tangy, spicy twist to everyday favorites."/>
+    <s v="Dry Red Chilly, Chickpea, Urad Dal, Tamarind, Garlic, Coriander, Cumin, Salt, Ghee, Ginger, Jaggery, Curry Leaf"/>
+    <s v="Enjoy this hotel-style blend of roasted dals, fiery chilies, and garlic. Mix it with ghee to dip soft idlis, or sprinkle it over a roasting dosa!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 14.95kcal, Protein 0.63g, Total Fat 0.47g, Saturated Fat 0.15g, Carbs 2.47g, Fiber 0.91g, Sugars 0.52g, Sodium 0.11g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="135"/>
+    <n v="135"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="285b7b12-59d1-47a0-afb2-986c6c72d045"/>
+    <m/>
+    <x v="12"/>
+    <s v="పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Palli Kaaram. Boldly Telugu!"/>
+    <s v="A nutty and spicy Kadapa classic made with peanuts, chili, and curry leaves. A true part of local culture — delicious with rice or even as a snack on its own."/>
+    <s v="Peanuts, Curry Leaf, Dry Red Chilly, Garlic, Red Chilly Powder, Salt, Cumin"/>
+    <s v="Add this unique Rayalaseema blend of roasted peanuts, garlic, and curry leaves to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 25.87kcal, Protein 1.24g, Total Fat 2.04g, Saturated Fat 0.36g, Carbs 1.02g, Fiber 0.64g, Sugars 0.2g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="135"/>
+    <n v="135"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="3d01988a-ad7d-4114-908b-38098cd63bd3"/>
+    <m/>
+    <x v="13"/>
+    <s v="పుదిన కారం"/>
+    <x v="0"/>
+    <s v="Light, Lively &amp; Minty-Perfect!"/>
+    <s v="A refreshing and aromatic South Indian spice blend featuring sun-dried mint, garlic, and roasted lentils for a zesty, herbaceous kick. This flavorful podi acts as a natural palate cleanser while providing a cooling, gut-friendly boost to your daily meals."/>
+    <s v="Red Chilly Powder, Mint Leaves, Urad Dal, Red Gram, Poha, Salt, Dry Red Chilly, Cumin, Tamarind, Jaggery"/>
+    <s v="Add this refreshing blend of mint leaves, roasted dals, and a hint of tamarind to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.89kcal, Protein 0.65g, Total Fat 0.26g, Saturated Fat 0.05g, Carbs 2.65g, Fiber 0.95g, Sugars 0.47g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="5d7272ee-37e6-43c3-bb9d-551dc2d7da38"/>
+    <m/>
+    <x v="14"/>
+    <s v=" పుట్నాల పొడి"/>
+    <x v="0"/>
+    <s v="Flavor-packed, protein-rich!"/>
+    <s v="A protein-rich lentil blend from Kadapa, this podi combines fried gram, coconut, and garlic for a nutty, savory taste. Traditionally enjoyed with pickle rice and ghee for an extra flavor boost."/>
+    <s v="Fried Gram, Dry Coconut, Garlic, Red Chilly Powder, Salt"/>
+    <s v="Add this classic blend of fried gram, dry coconut, and garlic to hot rice. Mix in a spoonful of ghee and pair with your favorite pickle for a perfect meal!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 18kcal, Protein 0.9g, Total Fat 0.55g, Saturated Fat 0.31g, Carbs 2.53g, Fiber 0.6g, Sugars 0.45g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="2cf104b5-c88f-48a7-9e5e-741a20cc2c20"/>
+    <m/>
+    <x v="15"/>
+    <s v="స్పెషల్ గోధుమ కారం"/>
+    <x v="0"/>
+    <s v="Tasty, Light &amp; Fresh!"/>
+    <s v="A wholesome, nutty podi made with chakki atta, dals, coconut, and garlic. Perfectly balanced, it brings a bold, hearty flavor to your meals."/>
+    <s v="Chakki Atta, Urad Dal, Red Chilly Powder, Dry Coconut, Flax Seed, Garlic, Salt"/>
+    <s v="Smear this unique, nutty mix of whole wheat, urad dal, and garlic onto dosas, or pair it with melted ghee for the perfect savory idli dip."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.24kcal, Protein 0.68g, Total Fat 0.41g, Saturated Fat 0.2g, Carbs 2.93g, Fiber 0.76g, Sugars 0.09g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="0219fa3e-9afc-4048-aba2-e9daa0fba81e"/>
+    <m/>
+    <x v="16"/>
+    <s v=" స్పెషల్ పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Rustic. Rich. Ridiculously Good!"/>
+    <s v="Our best-reviewed podi! A rustic blend of peanuts, coriander, and jaggery that delivers mellow, nutty flavors. Smooth and balanced, it’s even loved by kids when mixed with hot rice and ghee."/>
+    <s v="Peanuts, Fried Gram, Coriander, Jaggery, Dry Red Chilly, Salt, Tamarind"/>
+    <s v="Toss this flavorful mix of peanuts, fried gram, and coriander with hot rice and a good serving of ghee to beautifully bring out the sweet and tangy notes."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 19.99kcal, Protein 0.87g, Total Fat 1.03g, Saturated Fat 0.16g, Carbs 2.23g, Fiber 0.69g, Sugars 0.85g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="976a762d-59d8-421e-8a1a-dc0bd38850ea"/>
+    <m/>
+    <x v="17"/>
+    <s v="తమలపాకు కారం"/>
+    <x v="0"/>
+    <s v="Wellness in Every Bite – Betel Leaf at the Heart!"/>
+    <s v="A unique, health-focused herbal spice powder combining fresh betel leaves (Tamalapaaku) with traditional roasted spices and lentils."/>
+    <s v="Betel Leaf, Garlic, Urad Dal, Chickpea, Peanuts, Red Chilly Powder, Cumin, White Sesame Seeds, Coriander, Salt, Curry Leaf"/>
+    <s v="Stir this vibrantly fresh betel leaf and sesame mix into hot rice with a spoonful of ghee for an uplifting flavor."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.23kcal, Protein 0.66g, Total Fat 0.57g, Saturated Fat 0.09g, Carbs 1.64g, Fiber 0.65g, Sugars 0.16g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="220"/>
+    <n v="220"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="6bb57327-d5c7-4a3f-b645-031fe220a609"/>
+    <m/>
+    <x v="18"/>
+    <s v="వెల్లుల్లి కారం"/>
+    <x v="0"/>
+    <s v="Three Ingredients. Infinite Flavor!"/>
+    <s v="A garlicky podi with dry coconut and spices, a staple in every Kadapa household. Adds delicious flavor to sautéed vegetables or can be used as a base for curries."/>
+    <s v="Garlic, Red Chilly Powder, Salt, Sunflower Oil"/>
+    <s v="Smear this savory garlic blend onto hot dosas, or toss it with hot rice and ghee to bring out the roasted aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 10.59kcal, Protein 0.42g, Total Fat 0.45g, Saturated Fat 0.07g, Carbs 1.77g, Fiber 0.75g, Sugars 0.17g, Sodium 0.25g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="145"/>
+    <n v="145"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="81095baa-0101-4c50-8749-051c376d8fd8"/>
+    <m/>
+    <x v="19"/>
+    <s v="చట్నీ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Fresh Chutney in a Snap!"/>
+    <s v="A quick and easy blend of peanuts, gram, and spices. Just add water and grind to make a smooth, flavorful Palli (groundnut) chutney in minutes."/>
+    <s v="Peanuts, Fried Gram, Dry Red Chilly, Salt, Ginger, Tamarind, Coriander Powder"/>
+    <s v="Simply add water gradually to this flavorful blend until you reach your desired consistency.Ready in seconds to pair with hot tiffin."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 178.61kcal, Protein 9.01g, Total Fat 10.89g, Saturated Fat 1.83g, Carbs 13.74g, Fiber 5.08g, Sugars 2.74g, Sodium 0.64g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="9b6b3df2-7a39-407f-b320-9d6f6e9b0db9"/>
+    <m/>
+    <x v="20"/>
+    <s v="మల్టీ గ్రెయిన్ మిక్స్"/>
+    <x v="1"/>
+    <s v="Power of 13 Grains, Strength in Every Bite!"/>
+    <s v="A wholesome blend of 13 grains and legumes, designed to make multigrain chapatis at home. Nutritious and flavorful, it turns every bite into a healthy delight."/>
+    <s v="Horse Gram, Red Gram, Cornflour, Oats, Finger Millet, Soybean, Pearl Millet, Chickpea, Mung Bean, White Sesame Seeds, Urad Dal, Red Chilly Powder, Garlic, Coriander"/>
+    <s v="Add this mix to chakki atta in 1:5 ratio before making the dough, to get the health benefits of 13 grains in every bite."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 146.89kcal, Protein 7.23g, Total Fat 2.84g, Saturated Fat 0.42g, Carbs 23.55g, Fiber 4.57g, Sugars 0.89g, Sodium 0.04g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="95"/>
+    <n v="95"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="21685c21-498d-43b2-88ea-5a64964d64e8"/>
+    <m/>
+    <x v="21"/>
+    <s v="సాంబార్ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Authentic Sambar in a Snap!"/>
+    <s v="A convenient, ready-to-use blend of rice, lentils, spices, and tamarind. Just add vegetables and boil to enjoy a flavorful, authentic South Indian sambar in minutes."/>
+    <s v="Rice, Dry Red Chilly, Coriander, Red Gram, Urad Dal, Chickpea, Tamarind, Salt, Dry Coconut, Cumin, Fenugreek, Cinnamon, Curry Leaf"/>
+    <s v="Add 40g of this authentic blend to 1 liter of water along with your favorite fresh vegetables. Boil until tender for fresh sambar."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 127.92kcal, Protein 5.03g, Total Fat 3.08g, Saturated Fat 1.3g, Carbs 22.92g, Fiber 7.42g, Sugars 2.16g, Sodium 1.13g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="cc119ff6-8f5b-4913-97a1-fb2a95cb2989"/>
+    <m/>
+    <x v="22"/>
+    <s v="పెరి పెరి మసాలా"/>
+    <x v="1"/>
+    <s v="Fiery, Tangy, Totally Irresistible!"/>
+    <s v="A fiery, zesty fusion blend of African bird's eye chilies, garlic, herbs, and spices. Perfect for fries, chips, and snacks."/>
+    <s v="Sugar, Salt, Red Chilly Powder, Onion Powder, Kashmiri Red Chilly Powder, Garlic Powder, Amchur Powder, Black Pepper, Oregano"/>
+    <s v="Dust this zesty chili and herb mix generously over popcorn, makhana, or roasted nuts for a perfectly spicy snack."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.46kcal, Protein 0.32g, Total Fat 0.14g, Saturated Fat 0.04g, Carbs 3.08g, Fiber 0.6g, Sugars 0.92g, Sodium 0.3g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="1"/>
+    <n v="195"/>
+    <n v="195"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="d40333db-fc45-4a73-9329-eb54ef6a85b5"/>
+    <m/>
+    <x v="0"/>
+    <s v="అవిసగింజల కారం"/>
+    <x v="0"/>
+    <s v="Healthy Bite, Enriched with Ragi!"/>
+    <s v="A wholesome podi enriched with flax seeds and finger millet (ragi). Nutty, spicy, and lightly sweet, it delivers nutrition and taste in every bite."/>
+    <s v="Flax Seed, Urad Dal, Peanuts, Finger Millet, Dry Red Chilly, Salt, Garlic, Cloves, Tamarind, Jaggery, Cardamom, Curry Leaf, Cinnamon"/>
+    <s v="Add the desired amount of podi to hot rice. Mix in a spoonful of ghee to enhance the flavor and aroma. Serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.84kcal, Protein 0.85g, Total Fat 1.13g, Saturated Fat 0.14g, Carbs 2.03g, Fiber 1.1g, Sugars 0.21g, Sodium 0.1g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="255"/>
+    <n v="255"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="a72fb41d-834f-4e95-8207-933ee4ce2a47"/>
+    <m/>
+    <x v="1"/>
+    <s v="చింతాకు పొడి"/>
+    <x v="0"/>
+    <s v="Tangy. Nutty. Traditionally Bold!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Peanuts, Black Sesame Seeds, Tamarind Leaves, Dry Red Chilly, Garlic, Coriander, Salt"/>
+    <s v="Add this tangy blend of chinthaku, roasted peanuts, and black sesame to hot rice. Mix in a good serving of ghee and serve warm."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 24.99kcal, Protein 0.96g, Total Fat 1.86g, Saturated Fat 0.3g, Carbs 1.46g, Fiber 0.61g, Sugars 0.13g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="325"/>
+    <n v="325"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="5fd5ad76-ce6b-4a27-b189-bd32180f3c7c"/>
+    <m/>
+    <x v="2"/>
+    <s v="దోశ కారం"/>
+    <x v="0"/>
+    <s v="Perfect Spice for Crispy Dosas!"/>
+    <s v="A flavorful podi crafted for crispy dosas. Made with poha, lentils, and aromatic spices, it adds a nutty, spicy kick that enhances every bite with ghee."/>
+    <s v="Poha, Chickpea, Urad Dal, Coriander, Red Chilly Powder, Dry Red Chilly, Salt, Cumin, Curry Leaf, Garlic, Marathi Moggu, Cinnamon"/>
+    <s v="Evenly dust this vibrant mix of [Ingredient 1] and spices onto your roasting dosa. Finish with a touch of ghee for a spicy, flavorful bite."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.16kcal, Protein 0.67g, Total Fat 0.2g, Saturated Fat 0.02g, Carbs 3.13g, Fiber 0.83g, Sugars 0.17g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="210"/>
+    <n v="210"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="031d0c4a-11ea-49ab-aae9-b7b7d05bd29e"/>
+    <m/>
+    <x v="3"/>
+    <s v="కడప కారం"/>
+    <x v="0"/>
+    <s v="Bold flavor, rich and hearty!"/>
+    <s v="A signature Andhra blend that balances peanuts, garlic, and dry coconut with a fiery kick of red chili. Rich, hearty, and versatile — a true taste of Kadapa tradition."/>
+    <s v="Peanuts, Garlic, Dry Coconut, Cumin, Dry Red Chilly, Coriander, Jaggery, Salt, Red Chilly Powder, Curry Leaf, Lemon Salt"/>
+    <s v="Sprinkle this versatile, sweet-and-spicy blend of peanuts, garlic, and dry coconut over dosas, or mix it into hot rice with ghee. "/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.88kcal, Protein 0.7g, Total Fat 1.49g, Saturated Fat 0.75g, Carbs 1.51g, Fiber 0.64g, Sugars 0.31g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="NEW"/>
+    <s v="ADD"/>
+    <x v="4"/>
+    <s v="కంది పొడి"/>
+    <x v="0"/>
+    <s v="Roasted Lentils,.Pure Comfort!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Red Gram, Chickpea, Dry Red Chilly, Coriander, Urad Dal, Garlic, Cumin, Curry Leaf, White Sesame Seeds, Salt, Mung Bean, Fresh Coriander, Red Chilly Powder, Asafoetida"/>
+    <s v="Enjoy the traditional flavor of this multipurpose blend of roasted dals, garlic, and a hint of hing. Mix it into hot rice with a spoonful of ghee, or pair it with your daily tiffins!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.02kcal, Protein 0.92g, Total Fat 0.29g, Saturated Fat 0.04g, Carbs 2.71g, Fiber 0.92g, Sugars 0.12g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="255"/>
+    <n v="255"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="d4eb273f-08a8-4f6b-bfac-8c4dce9c5511"/>
+    <m/>
+    <x v="5"/>
+    <s v="కరివేపాకు పొడి"/>
+    <x v="0"/>
+    <s v="Earthy.Spicy. Naturally Good!"/>
+    <s v="A must-try Andhra specialty made with fragrant curry leaves, dals, and spices. Earthy and wholesome, this podi pairs beautifully with hot rice and ghee for a nourishing meal."/>
+    <s v="Curry Leaf, Garlic, Urad Dal, Dry Red Chilly, Chickpea, Coriander, Tamarind, Salt, Cumin, Fenugreek"/>
+    <s v="Mix the desired amount of this earthy curry leaf, garlic, and tamarind blend into hot rice. Stir in a generous serving of ghee for a comforting, traditional meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.71kcal, Protein 0.81g, Total Fat 0.2g, Saturated Fat 0.05g, Carbs 2.39g, Fiber 1.33g, Sugars 0.23g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="38b67b7f-2441-4024-88f1-f3f0c0a29d00"/>
+    <m/>
+    <x v="6"/>
+    <s v="కర్ణాటక ఇడ్లీ పొడి"/>
+    <x v="0"/>
+    <s v="Idli’s Best Friends: Ghee &amp; Podi!"/>
+    <s v="A classic South Indian podi made with chickpeas, urad dal, and spices. Perfectly balanced for hot idlis with ghee, adding a nutty, mildly spicy flavor every time."/>
+    <s v="Chickpea, Urad Dal, Dry Red Chilly, Salt, Cumin, Black Pepper, Red Chilly Powder, Curry Leaf"/>
+    <s v="Mix this classic blend of roasted dals and black pepper with a generous spoonful of ghee. Spread it right on top for a perfect bite!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.22kcal, Protein 1.03g, Total Fat 0.16g, Saturated Fat 0.02g, Carbs 2.91g, Fiber 1.02g, Sugars 0.32g, Sodium 0.08g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="230"/>
+    <n v="230"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="05dd8c31-48da-4ea0-84bd-345c7c25b5f9"/>
+    <m/>
+    <x v="7"/>
+    <s v="కోనసీమ కారం"/>
+    <x v="0"/>
+    <s v="Superfoods Meet Fiery Tradition!"/>
+    <s v="A signature spice blend inspired by the coastal Konaseema region. Blends dry coconut, garlic, and red chilies for a rich, aromatic flavor."/>
+    <s v="Curry Leaf, Flax Seed, Peanuts, Moringa, Dry Red Chilly, Chickpea, Coriander, Raisin, Fresh Mint, Tamarind, Urad Dal, White Sesame Seeds, Salt, Ginger, Asafoetida"/>
+    <s v="Place Holder"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 15.47kcal, Protein 0.81g, Total Fat 0.71g, Saturated Fat 0.11g, Carbs 1.88g, Fiber 1.1g, Sugars 0.35g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="30"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="350"/>
+    <n v="350"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="7421e0f3-7316-47eb-b75c-c5d92763b9fd"/>
+    <m/>
+    <x v="8"/>
+    <s v="కూర కారం"/>
+    <x v="0"/>
+    <s v="Sauté. Sprinkle. Savor Garlic!"/>
+    <s v="The essential Telugu multi-purpose spice mix used for seasoning daily curries, fries, and gravies. Perfect balance of spices."/>
+    <s v="Dry Coconut, Garlic, Red Chilly Powder, Coriander, Salt"/>
+    <s v="Sauté your everyday vegetables, sprinkle this rich blend of garlic and dry coconut over the top, and savor the bold flavor!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.76kcal, Protein 0.39g, Total Fat 1.64g, Saturated Fat 1.37g, Carbs 1.55g, Fiber 0.95g, Sugars 0.23g, Sodium 0.2g"/>
+    <b v="0"/>
+    <b v="0"/>
+    <n v="45"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="98df3516-f8f6-4379-b45e-513b78971171"/>
+    <m/>
+    <x v="9"/>
+    <s v="కొత్తిమీర కారం"/>
+    <x v="0"/>
+    <s v="Zesty coriander Spark – Freshness in Every Spoon!"/>
+    <s v="A vibrant, aromatic spice powder made with fresh sun-dried coriander leaves, roasted dals, and garlic. Earthy and fresh."/>
+    <s v="Red Chilly Powder, Fresh Coriander, Red Gram, Urad Dal, Salt, Poha, Dry Red Chilly, Cumin, Jaggery, Tamarind"/>
+    <s v="Toss this flavorful mix of coriander and roasted dals with hot rice and ghee to bring out the rich, herby aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.34kcal, Protein 0.54g, Total Fat 0.23g, Saturated Fat 0.04g, Carbs 2.37g, Fiber 0.77g, Sugars 0.48g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="581f07ae-4d33-4fa1-8915-655e48c183c3"/>
+    <m/>
+    <x v="10"/>
+    <s v="మునగాకు కారం"/>
+    <x v="0"/>
+    <s v="Moringa Magic: Nutritious. Natural. Delicious!"/>
+    <s v="A nutrient-dense South Indian spice blend combining superfood Moringa leaves with roasted lentils and seeds for a savory, earthy flavor. This all-natural &quot;miracle podi&quot; delivers a potent boost of vitamins and antioxidants in every spoonful."/>
+    <s v="Red Gram, Moringa, Chickpea, Pumpkin Seeds, Salt, Dry Red Chilly, Cumin, Black Pepper, Curry Leaf, Mint Leaves, Lemon Salt"/>
+    <s v="Mix the desired amount of this moringa, pumpkin seed blend into hot rice. Stir in a generous serving of ghee for a nutritious meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.43kcal, Protein 0.85g, Total Fat 0.39g, Saturated Fat 0.06g, Carbs 1.85g, Fiber 0.62g, Sugars 0.09g, Sodium 0.22g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="300"/>
+    <n v="300"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ba2fe49f-75f1-4db0-b2d0-edd26d81cc62"/>
+    <m/>
+    <x v="11"/>
+    <s v="నల్ల కారం"/>
+    <x v="0"/>
+    <s v="High fiber, gut-friendly spice!"/>
+    <s v="A wholesome Andhra classic made with tamarind, dals, and garlic. High in fiber and flavor, this podi adds a tangy, spicy twist to everyday favorites."/>
+    <s v="Dry Red Chilly, Chickpea, Urad Dal, Tamarind, Garlic, Coriander, Cumin, Salt, Ghee, Ginger, Jaggery, Curry Leaf"/>
+    <s v="Enjoy this hotel-style blend of roasted dals, fiery chilies, and garlic. Mix it with ghee to dip soft idlis, or sprinkle it over a roasting dosa!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 14.95kcal, Protein 0.63g, Total Fat 0.47g, Saturated Fat 0.15g, Carbs 2.47g, Fiber 0.91g, Sugars 0.52g, Sodium 0.11g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="255"/>
+    <n v="255"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="285b7b12-59d1-47a0-afb2-986c6c72d045"/>
+    <m/>
+    <x v="12"/>
+    <s v="పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Palli Kaaram. Boldly Telugu!"/>
+    <s v="A nutty and spicy Kadapa classic made with peanuts, chili, and curry leaves. A true part of local culture — delicious with rice or even as a snack on its own."/>
+    <s v="Peanuts, Curry Leaf, Dry Red Chilly, Garlic, Red Chilly Powder, Salt, Cumin"/>
+    <s v="Add this unique Rayalaseema blend of roasted peanuts, garlic, and curry leaves to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 25.87kcal, Protein 1.24g, Total Fat 2.04g, Saturated Fat 0.36g, Carbs 1.02g, Fiber 0.64g, Sugars 0.2g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="255"/>
+    <n v="255"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="3d01988a-ad7d-4114-908b-38098cd63bd3"/>
+    <m/>
+    <x v="13"/>
+    <s v="పుదిన కారం"/>
+    <x v="0"/>
+    <s v="Light, Lively &amp; Minty-Perfect!"/>
+    <s v="A refreshing and aromatic South Indian spice blend featuring sun-dried mint, garlic, and roasted lentils for a zesty, herbaceous kick. This flavorful podi acts as a natural palate cleanser while providing a cooling, gut-friendly boost to your daily meals."/>
+    <s v="Red Chilly Powder, Mint Leaves, Urad Dal, Red Gram, Poha, Salt, Dry Red Chilly, Cumin, Tamarind, Jaggery"/>
+    <s v="Add this refreshing blend of mint leaves, roasted dals, and a hint of tamarind to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.89kcal, Protein 0.65g, Total Fat 0.26g, Saturated Fat 0.05g, Carbs 2.65g, Fiber 0.95g, Sugars 0.47g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="5d7272ee-37e6-43c3-bb9d-551dc2d7da38"/>
+    <m/>
+    <x v="14"/>
+    <s v=" పుట్నాల పొడి"/>
+    <x v="0"/>
+    <s v="Flavor-packed, protein-rich!"/>
+    <s v="A protein-rich lentil blend from Kadapa, this podi combines fried gram, coconut, and garlic for a nutty, savory taste. Traditionally enjoyed with pickle rice and ghee for an extra flavor boost."/>
+    <s v="Fried Gram, Dry Coconut, Garlic, Red Chilly Powder, Salt"/>
+    <s v="Add this classic blend of fried gram, dry coconut, and garlic to hot rice. Mix in a spoonful of ghee and pair with your favorite pickle for a perfect meal!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 18kcal, Protein 0.9g, Total Fat 0.55g, Saturated Fat 0.31g, Carbs 2.53g, Fiber 0.6g, Sugars 0.45g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="230"/>
+    <n v="230"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2cf104b5-c88f-48a7-9e5e-741a20cc2c20"/>
+    <m/>
+    <x v="15"/>
+    <s v="స్పెషల్ గోధుమ కారం"/>
+    <x v="0"/>
+    <s v="Tasty, Light &amp; Fresh!"/>
+    <s v="A wholesome, nutty podi made with chakki atta, dals, coconut, and garlic. Perfectly balanced, it brings a bold, hearty flavor to your meals."/>
+    <s v="Chakki Atta, Urad Dal, Red Chilly Powder, Dry Coconut, Flax Seed, Garlic, Salt"/>
+    <s v="Smear this unique, nutty mix of whole wheat, urad dal, and garlic onto dosas, or pair it with melted ghee for the perfect savory idli dip."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.24kcal, Protein 0.68g, Total Fat 0.41g, Saturated Fat 0.2g, Carbs 2.93g, Fiber 0.76g, Sugars 0.09g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="210"/>
+    <n v="210"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="0219fa3e-9afc-4048-aba2-e9daa0fba81e"/>
+    <m/>
+    <x v="16"/>
+    <s v=" స్పెషల్ పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Rustic. Rich. Ridiculously Good!"/>
+    <s v="Our best-reviewed podi! A rustic blend of peanuts, coriander, and jaggery that delivers mellow, nutty flavors. Smooth and balanced, it’s even loved by kids when mixed with hot rice and ghee."/>
+    <s v="Peanuts, Fried Gram, Coriander, Jaggery, Dry Red Chilly, Salt, Tamarind"/>
+    <s v="Toss this flavorful mix of peanuts, fried gram, and coriander with hot rice and a good serving of ghee to beautifully bring out the sweet and tangy notes."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 19.99kcal, Protein 0.87g, Total Fat 1.03g, Saturated Fat 0.16g, Carbs 2.23g, Fiber 0.69g, Sugars 0.85g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="976a762d-59d8-421e-8a1a-dc0bd38850ea"/>
+    <m/>
+    <x v="17"/>
+    <s v="తమలపాకు కారం"/>
+    <x v="0"/>
+    <s v="Wellness in Every Bite – Betel Leaf at the Heart!"/>
+    <s v="A unique, health-focused herbal spice powder combining fresh betel leaves (Tamalapaaku) with traditional roasted spices and lentils."/>
+    <s v="Betel Leaf, Garlic, Urad Dal, Chickpea, Peanuts, Red Chilly Powder, Cumin, White Sesame Seeds, Coriander, Salt, Curry Leaf"/>
+    <s v="Stir this vibrantly fresh betel leaf and sesame mix into hot rice with a spoonful of ghee for an uplifting flavor."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.23kcal, Protein 0.66g, Total Fat 0.57g, Saturated Fat 0.09g, Carbs 1.64g, Fiber 0.65g, Sugars 0.16g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="420"/>
+    <n v="420"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="6bb57327-d5c7-4a3f-b645-031fe220a609"/>
+    <m/>
+    <x v="18"/>
+    <s v="వెల్లుల్లి కారం"/>
+    <x v="0"/>
+    <s v="Three Ingredients. Infinite Flavor!"/>
+    <s v="A garlicky podi with dry coconut and spices, a staple in every Kadapa household. Adds delicious flavor to sautéed vegetables or can be used as a base for curries."/>
+    <s v="Garlic, Red Chilly Powder, Salt, Sunflower Oil"/>
+    <s v="Smear this savory garlic blend onto hot dosas, or toss it with hot rice and ghee to bring out the roasted aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 10.59kcal, Protein 0.42g, Total Fat 0.45g, Saturated Fat 0.07g, Carbs 1.77g, Fiber 0.75g, Sugars 0.17g, Sodium 0.25g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="280"/>
+    <n v="280"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="81095baa-0101-4c50-8749-051c376d8fd8"/>
+    <m/>
+    <x v="19"/>
+    <s v="చట్నీ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Fresh Chutney in a Snap!"/>
+    <s v="A quick and easy blend of peanuts, gram, and spices. Just add water and grind to make a smooth, flavorful Palli (groundnut) chutney in minutes."/>
+    <s v="Peanuts, Fried Gram, Dry Red Chilly, Salt, Ginger, Tamarind, Coriander Powder"/>
+    <s v="Simply add water gradually to this flavorful blend until you reach your desired consistency.Ready in seconds to pair with hot tiffin."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 178.61kcal, Protein 9.01g, Total Fat 10.89g, Saturated Fat 1.83g, Carbs 13.74g, Fiber 5.08g, Sugars 2.74g, Sodium 0.64g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="210"/>
+    <n v="210"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="9b6b3df2-7a39-407f-b320-9d6f6e9b0db9"/>
+    <m/>
+    <x v="20"/>
+    <s v="మల్టీ గ్రెయిన్ మిక్స్"/>
+    <x v="1"/>
+    <s v="Power of 13 Grains, Strength in Every Bite!"/>
+    <s v="A wholesome blend of 13 grains and legumes, designed to make multigrain chapatis at home. Nutritious and flavorful, it turns every bite into a healthy delight."/>
+    <s v="Horse Gram, Red Gram, Cornflour, Oats, Finger Millet, Soybean, Pearl Millet, Chickpea, Mung Bean, White Sesame Seeds, Urad Dal, Red Chilly Powder, Garlic, Coriander"/>
+    <s v="Add this mix to chakki atta in 1:5 ratio before making the dough, to get the health benefits of 13 grains in every bite."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 146.89kcal, Protein 7.23g, Total Fat 2.84g, Saturated Fat 0.42g, Carbs 23.55g, Fiber 4.57g, Sugars 0.89g, Sodium 0.04g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="185"/>
+    <n v="185"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="21685c21-498d-43b2-88ea-5a64964d64e8"/>
+    <m/>
+    <x v="21"/>
+    <s v="సాంబార్ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Authentic Sambar in a Snap!"/>
+    <s v="A convenient, ready-to-use blend of rice, lentils, spices, and tamarind. Just add vegetables and boil to enjoy a flavorful, authentic South Indian sambar in minutes."/>
+    <s v="Rice, Dry Red Chilly, Coriander, Red Gram, Urad Dal, Chickpea, Tamarind, Salt, Dry Coconut, Cumin, Fenugreek, Cinnamon, Curry Leaf"/>
+    <s v="Add 40g of this authentic blend to 1 liter of water along with your favorite fresh vegetables. Boil until tender for fresh sambar."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 127.92kcal, Protein 5.03g, Total Fat 3.08g, Saturated Fat 1.3g, Carbs 22.92g, Fiber 7.42g, Sugars 2.16g, Sodium 1.13g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="230"/>
+    <n v="230"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="cc119ff6-8f5b-4913-97a1-fb2a95cb2989"/>
+    <m/>
+    <x v="22"/>
+    <s v="పెరి పెరి మసాలా"/>
+    <x v="1"/>
+    <s v="Fiery, Tangy, Totally Irresistible!"/>
+    <s v="A fiery, zesty fusion blend of African bird's eye chilies, garlic, herbs, and spices. Perfect for fries, chips, and snacks."/>
+    <s v="Sugar, Salt, Red Chilly Powder, Onion Powder, Kashmiri Red Chilly Powder, Garlic Powder, Amchur Powder, Black Pepper, Oregano"/>
+    <s v="Dust this zesty chili and herb mix generously over popcorn, makhana, or roasted nuts for a perfectly spicy snack."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.46kcal, Protein 0.32g, Total Fat 0.14g, Saturated Fat 0.04g, Carbs 3.08g, Fiber 0.6g, Sugars 0.92g, Sodium 0.3g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="2"/>
+    <n v="370"/>
+    <n v="370"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="d40333db-fc45-4a73-9329-eb54ef6a85b5"/>
+    <m/>
+    <x v="0"/>
+    <s v="అవిసగింజల కారం"/>
+    <x v="0"/>
+    <s v="Healthy Bite, Enriched with Ragi!"/>
+    <s v="A wholesome podi enriched with flax seeds and finger millet (ragi). Nutty, spicy, and lightly sweet, it delivers nutrition and taste in every bite."/>
+    <s v="Flax Seed, Urad Dal, Peanuts, Finger Millet, Dry Red Chilly, Salt, Garlic, Cloves, Tamarind, Jaggery, Cardamom, Curry Leaf, Cinnamon"/>
+    <s v="Add the desired amount of podi to hot rice. Mix in a spoonful of ghee to enhance the flavor and aroma. Serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.84kcal, Protein 0.85g, Total Fat 1.13g, Saturated Fat 0.14g, Carbs 2.03g, Fiber 1.1g, Sugars 0.21g, Sodium 0.1g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="495"/>
+    <n v="495"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="a72fb41d-834f-4e95-8207-933ee4ce2a47"/>
+    <m/>
+    <x v="1"/>
+    <s v="చింతాకు పొడి"/>
+    <x v="0"/>
+    <s v="Tangy. Nutty. Traditionally Bold!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Peanuts, Black Sesame Seeds, Tamarind Leaves, Dry Red Chilly, Garlic, Coriander, Salt"/>
+    <s v="Add this tangy blend of chinthaku, roasted peanuts, and black sesame to hot rice. Mix in a good serving of ghee and serve warm."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 24.99kcal, Protein 0.96g, Total Fat 1.86g, Saturated Fat 0.3g, Carbs 1.46g, Fiber 0.61g, Sugars 0.13g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="630"/>
+    <n v="630"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="5fd5ad76-ce6b-4a27-b189-bd32180f3c7c"/>
+    <m/>
+    <x v="2"/>
+    <s v="దోశ కారం"/>
+    <x v="0"/>
+    <s v="Perfect Spice for Crispy Dosas!"/>
+    <s v="A flavorful podi crafted for crispy dosas. Made with poha, lentils, and aromatic spices, it adds a nutty, spicy kick that enhances every bite with ghee."/>
+    <s v="Poha, Chickpea, Urad Dal, Coriander, Red Chilly Powder, Dry Red Chilly, Salt, Cumin, Curry Leaf, Garlic, Marathi Moggu, Cinnamon"/>
+    <s v="Evenly dust this vibrant mix of [Ingredient 1] and spices onto your roasting dosa. Finish with a touch of ghee for a spicy, flavorful bite."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.16kcal, Protein 0.67g, Total Fat 0.2g, Saturated Fat 0.02g, Carbs 3.13g, Fiber 0.83g, Sugars 0.17g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="405"/>
+    <n v="405"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="031d0c4a-11ea-49ab-aae9-b7b7d05bd29e"/>
+    <m/>
+    <x v="3"/>
+    <s v="కడప కారం"/>
+    <x v="0"/>
+    <s v="Bold flavor, rich and hearty!"/>
+    <s v="A signature Andhra blend that balances peanuts, garlic, and dry coconut with a fiery kick of red chili. Rich, hearty, and versatile — a true taste of Kadapa tradition."/>
+    <s v="Peanuts, Garlic, Dry Coconut, Cumin, Dry Red Chilly, Coriander, Jaggery, Salt, Red Chilly Powder, Curry Leaf, Lemon Salt"/>
+    <s v="Sprinkle this versatile, sweet-and-spicy blend of peanuts, garlic, and dry coconut over dosas, or mix it into hot rice with ghee. "/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.88kcal, Protein 0.7g, Total Fat 1.49g, Saturated Fat 0.75g, Carbs 1.51g, Fiber 0.64g, Sugars 0.31g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="NEW"/>
+    <s v="ADD"/>
+    <x v="4"/>
+    <s v="కంది పొడి"/>
+    <x v="0"/>
+    <s v="Roasted Lentils,.Pure Comfort!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Red Gram, Chickpea, Dry Red Chilly, Coriander, Urad Dal, Garlic, Cumin, Curry Leaf, White Sesame Seeds, Salt, Mung Bean, Fresh Coriander, Red Chilly Powder, Asafoetida"/>
+    <s v="Enjoy the traditional flavor of this multipurpose blend of roasted dals, garlic, and a hint of hing. Mix it into hot rice with a spoonful of ghee, or pair it with your daily tiffins!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.02kcal, Protein 0.92g, Total Fat 0.29g, Saturated Fat 0.04g, Carbs 2.71g, Fiber 0.92g, Sugars 0.12g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="495"/>
+    <n v="495"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="d4eb273f-08a8-4f6b-bfac-8c4dce9c5511"/>
+    <m/>
+    <x v="5"/>
+    <s v="కరివేపాకు పొడి"/>
+    <x v="0"/>
+    <s v="Earthy.Spicy. Naturally Good!"/>
+    <s v="A must-try Andhra specialty made with fragrant curry leaves, dals, and spices. Earthy and wholesome, this podi pairs beautifully with hot rice and ghee for a nourishing meal."/>
+    <s v="Curry Leaf, Garlic, Urad Dal, Dry Red Chilly, Chickpea, Coriander, Tamarind, Salt, Cumin, Fenugreek"/>
+    <s v="Mix the desired amount of this earthy curry leaf, garlic, and tamarind blend into hot rice. Stir in a generous serving of ghee for a comforting, traditional meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.71kcal, Protein 0.81g, Total Fat 0.2g, Saturated Fat 0.05g, Carbs 2.39g, Fiber 1.33g, Sugars 0.23g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="38b67b7f-2441-4024-88f1-f3f0c0a29d00"/>
+    <m/>
+    <x v="6"/>
+    <s v="కర్ణాటక ఇడ్లీ పొడి"/>
+    <x v="0"/>
+    <s v="Idli’s Best Friends: Ghee &amp; Podi!"/>
+    <s v="A classic South Indian podi made with chickpeas, urad dal, and spices. Perfectly balanced for hot idlis with ghee, adding a nutty, mildly spicy flavor every time."/>
+    <s v="Chickpea, Urad Dal, Dry Red Chilly, Salt, Cumin, Black Pepper, Red Chilly Powder, Curry Leaf"/>
+    <s v="Mix this classic blend of roasted dals and black pepper with a generous spoonful of ghee. Spread it right on top for a perfect bite!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.22kcal, Protein 1.03g, Total Fat 0.16g, Saturated Fat 0.02g, Carbs 2.91g, Fiber 1.02g, Sugars 0.32g, Sodium 0.08g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="450"/>
+    <n v="450"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="05dd8c31-48da-4ea0-84bd-345c7c25b5f9"/>
+    <m/>
+    <x v="7"/>
+    <s v="కోనసీమ కారం"/>
+    <x v="0"/>
+    <s v="Superfoods Meet Fiery Tradition!"/>
+    <s v="A signature spice blend inspired by the coastal Konaseema region. Blends dry coconut, garlic, and red chilies for a rich, aromatic flavor."/>
+    <s v="Curry Leaf, Flax Seed, Peanuts, Moringa, Dry Red Chilly, Chickpea, Coriander, Raisin, Fresh Mint, Tamarind, Urad Dal, White Sesame Seeds, Salt, Ginger, Asafoetida"/>
+    <s v="Place Holder"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 15.47kcal, Protein 0.81g, Total Fat 0.71g, Saturated Fat 0.11g, Carbs 1.88g, Fiber 1.1g, Sugars 0.35g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="30"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="675"/>
+    <n v="675"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="7421e0f3-7316-47eb-b75c-c5d92763b9fd"/>
+    <m/>
+    <x v="8"/>
+    <s v="కూర కారం"/>
+    <x v="0"/>
+    <s v="Sauté. Sprinkle. Savor Garlic!"/>
+    <s v="The essential Telugu multi-purpose spice mix used for seasoning daily curries, fries, and gravies. Perfect balance of spices."/>
+    <s v="Dry Coconut, Garlic, Red Chilly Powder, Coriander, Salt"/>
+    <s v="Sauté your everyday vegetables, sprinkle this rich blend of garlic and dry coconut over the top, and savor the bold flavor!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.76kcal, Protein 0.39g, Total Fat 1.64g, Saturated Fat 1.37g, Carbs 1.55g, Fiber 0.95g, Sugars 0.23g, Sodium 0.2g"/>
+    <b v="0"/>
+    <b v="0"/>
+    <n v="45"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="98df3516-f8f6-4379-b45e-513b78971171"/>
+    <m/>
+    <x v="9"/>
+    <s v="కొత్తిమీర కారం"/>
+    <x v="0"/>
+    <s v="Zesty coriander Spark – Freshness in Every Spoon!"/>
+    <s v="A vibrant, aromatic spice powder made with fresh sun-dried coriander leaves, roasted dals, and garlic. Earthy and fresh."/>
+    <s v="Red Chilly Powder, Fresh Coriander, Red Gram, Urad Dal, Salt, Poha, Dry Red Chilly, Cumin, Jaggery, Tamarind"/>
+    <s v="Toss this flavorful mix of coriander and roasted dals with hot rice and ghee to bring out the rich, herby aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.34kcal, Protein 0.54g, Total Fat 0.23g, Saturated Fat 0.04g, Carbs 2.37g, Fiber 0.77g, Sugars 0.48g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="581f07ae-4d33-4fa1-8915-655e48c183c3"/>
+    <m/>
+    <x v="10"/>
+    <s v="మునగాకు కారం"/>
+    <x v="0"/>
+    <s v="Moringa Magic: Nutritious. Natural. Delicious!"/>
+    <s v="A nutrient-dense South Indian spice blend combining superfood Moringa leaves with roasted lentils and seeds for a savory, earthy flavor. This all-natural &quot;miracle podi&quot; delivers a potent boost of vitamins and antioxidants in every spoonful."/>
+    <s v="Red Gram, Moringa, Chickpea, Pumpkin Seeds, Salt, Dry Red Chilly, Cumin, Black Pepper, Curry Leaf, Mint Leaves, Lemon Salt"/>
+    <s v="Mix the desired amount of this moringa, pumpkin seed blend into hot rice. Stir in a generous serving of ghee for a nutritious meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.43kcal, Protein 0.85g, Total Fat 0.39g, Saturated Fat 0.06g, Carbs 1.85g, Fiber 0.62g, Sugars 0.09g, Sodium 0.22g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="585"/>
+    <n v="585"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="ba2fe49f-75f1-4db0-b2d0-edd26d81cc62"/>
+    <m/>
+    <x v="11"/>
+    <s v="నల్ల కారం"/>
+    <x v="0"/>
+    <s v="High fiber, gut-friendly spice!"/>
+    <s v="A wholesome Andhra classic made with tamarind, dals, and garlic. High in fiber and flavor, this podi adds a tangy, spicy twist to everyday favorites."/>
+    <s v="Dry Red Chilly, Chickpea, Urad Dal, Tamarind, Garlic, Coriander, Cumin, Salt, Ghee, Ginger, Jaggery, Curry Leaf"/>
+    <s v="Enjoy this hotel-style blend of roasted dals, fiery chilies, and garlic. Mix it with ghee to dip soft idlis, or sprinkle it over a roasting dosa!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 14.95kcal, Protein 0.63g, Total Fat 0.47g, Saturated Fat 0.15g, Carbs 2.47g, Fiber 0.91g, Sugars 0.52g, Sodium 0.11g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="495"/>
+    <n v="495"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="285b7b12-59d1-47a0-afb2-986c6c72d045"/>
+    <m/>
+    <x v="12"/>
+    <s v="పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Palli Kaaram. Boldly Telugu!"/>
+    <s v="A nutty and spicy Kadapa classic made with peanuts, chili, and curry leaves. A true part of local culture — delicious with rice or even as a snack on its own."/>
+    <s v="Peanuts, Curry Leaf, Dry Red Chilly, Garlic, Red Chilly Powder, Salt, Cumin"/>
+    <s v="Add this unique Rayalaseema blend of roasted peanuts, garlic, and curry leaves to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 25.87kcal, Protein 1.24g, Total Fat 2.04g, Saturated Fat 0.36g, Carbs 1.02g, Fiber 0.64g, Sugars 0.2g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="495"/>
+    <n v="495"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="3d01988a-ad7d-4114-908b-38098cd63bd3"/>
+    <m/>
+    <x v="13"/>
+    <s v="పుదిన కారం"/>
+    <x v="0"/>
+    <s v="Light, Lively &amp; Minty-Perfect!"/>
+    <s v="A refreshing and aromatic South Indian spice blend featuring sun-dried mint, garlic, and roasted lentils for a zesty, herbaceous kick. This flavorful podi acts as a natural palate cleanser while providing a cooling, gut-friendly boost to your daily meals."/>
+    <s v="Red Chilly Powder, Mint Leaves, Urad Dal, Red Gram, Poha, Salt, Dry Red Chilly, Cumin, Tamarind, Jaggery"/>
+    <s v="Add this refreshing blend of mint leaves, roasted dals, and a hint of tamarind to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.89kcal, Protein 0.65g, Total Fat 0.26g, Saturated Fat 0.05g, Carbs 2.65g, Fiber 0.95g, Sugars 0.47g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="5d7272ee-37e6-43c3-bb9d-551dc2d7da38"/>
+    <m/>
+    <x v="14"/>
+    <s v=" పుట్నాల పొడి"/>
+    <x v="0"/>
+    <s v="Flavor-packed, protein-rich!"/>
+    <s v="A protein-rich lentil blend from Kadapa, this podi combines fried gram, coconut, and garlic for a nutty, savory taste. Traditionally enjoyed with pickle rice and ghee for an extra flavor boost."/>
+    <s v="Fried Gram, Dry Coconut, Garlic, Red Chilly Powder, Salt"/>
+    <s v="Add this classic blend of fried gram, dry coconut, and garlic to hot rice. Mix in a spoonful of ghee and pair with your favorite pickle for a perfect meal!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 18kcal, Protein 0.9g, Total Fat 0.55g, Saturated Fat 0.31g, Carbs 2.53g, Fiber 0.6g, Sugars 0.45g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="450"/>
+    <n v="450"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="2cf104b5-c88f-48a7-9e5e-741a20cc2c20"/>
+    <m/>
+    <x v="15"/>
+    <s v="స్పెషల్ గోధుమ కారం"/>
+    <x v="0"/>
+    <s v="Tasty, Light &amp; Fresh!"/>
+    <s v="A wholesome, nutty podi made with chakki atta, dals, coconut, and garlic. Perfectly balanced, it brings a bold, hearty flavor to your meals."/>
+    <s v="Chakki Atta, Urad Dal, Red Chilly Powder, Dry Coconut, Flax Seed, Garlic, Salt"/>
+    <s v="Smear this unique, nutty mix of whole wheat, urad dal, and garlic onto dosas, or pair it with melted ghee for the perfect savory idli dip."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.24kcal, Protein 0.68g, Total Fat 0.41g, Saturated Fat 0.2g, Carbs 2.93g, Fiber 0.76g, Sugars 0.09g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="405"/>
+    <n v="405"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="0219fa3e-9afc-4048-aba2-e9daa0fba81e"/>
+    <m/>
+    <x v="16"/>
+    <s v=" స్పెషల్ పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Rustic. Rich. Ridiculously Good!"/>
+    <s v="Our best-reviewed podi! A rustic blend of peanuts, coriander, and jaggery that delivers mellow, nutty flavors. Smooth and balanced, it’s even loved by kids when mixed with hot rice and ghee."/>
+    <s v="Peanuts, Fried Gram, Coriander, Jaggery, Dry Red Chilly, Salt, Tamarind"/>
+    <s v="Toss this flavorful mix of peanuts, fried gram, and coriander with hot rice and a good serving of ghee to beautifully bring out the sweet and tangy notes."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 19.99kcal, Protein 0.87g, Total Fat 1.03g, Saturated Fat 0.16g, Carbs 2.23g, Fiber 0.69g, Sugars 0.85g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="976a762d-59d8-421e-8a1a-dc0bd38850ea"/>
+    <m/>
+    <x v="17"/>
+    <s v="తమలపాకు కారం"/>
+    <x v="0"/>
+    <s v="Wellness in Every Bite – Betel Leaf at the Heart!"/>
+    <s v="A unique, health-focused herbal spice powder combining fresh betel leaves (Tamalapaaku) with traditional roasted spices and lentils."/>
+    <s v="Betel Leaf, Garlic, Urad Dal, Chickpea, Peanuts, Red Chilly Powder, Cumin, White Sesame Seeds, Coriander, Salt, Curry Leaf"/>
+    <s v="Stir this vibrantly fresh betel leaf and sesame mix into hot rice with a spoonful of ghee for an uplifting flavor."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.23kcal, Protein 0.66g, Total Fat 0.57g, Saturated Fat 0.09g, Carbs 1.64g, Fiber 0.65g, Sugars 0.16g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="810"/>
+    <n v="810"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="6bb57327-d5c7-4a3f-b645-031fe220a609"/>
+    <m/>
+    <x v="18"/>
+    <s v="వెల్లుల్లి కారం"/>
+    <x v="0"/>
+    <s v="Three Ingredients. Infinite Flavor!"/>
+    <s v="A garlicky podi with dry coconut and spices, a staple in every Kadapa household. Adds delicious flavor to sautéed vegetables or can be used as a base for curries."/>
+    <s v="Garlic, Red Chilly Powder, Salt, Sunflower Oil"/>
+    <s v="Smear this savory garlic blend onto hot dosas, or toss it with hot rice and ghee to bring out the roasted aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 10.59kcal, Protein 0.42g, Total Fat 0.45g, Saturated Fat 0.07g, Carbs 1.77g, Fiber 0.75g, Sugars 0.17g, Sodium 0.25g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="540"/>
+    <n v="540"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="81095baa-0101-4c50-8749-051c376d8fd8"/>
+    <m/>
+    <x v="19"/>
+    <s v="చట్నీ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Fresh Chutney in a Snap!"/>
+    <s v="A quick and easy blend of peanuts, gram, and spices. Just add water and grind to make a smooth, flavorful Palli (groundnut) chutney in minutes."/>
+    <s v="Peanuts, Fried Gram, Dry Red Chilly, Salt, Ginger, Tamarind, Coriander Powder"/>
+    <s v="Simply add water gradually to this flavorful blend until you reach your desired consistency.Ready in seconds to pair with hot tiffin."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 178.61kcal, Protein 9.01g, Total Fat 10.89g, Saturated Fat 1.83g, Carbs 13.74g, Fiber 5.08g, Sugars 2.74g, Sodium 0.64g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="405"/>
+    <n v="405"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="9b6b3df2-7a39-407f-b320-9d6f6e9b0db9"/>
+    <m/>
+    <x v="20"/>
+    <s v="మల్టీ గ్రెయిన్ మిక్స్"/>
+    <x v="1"/>
+    <s v="Power of 13 Grains, Strength in Every Bite!"/>
+    <s v="A wholesome blend of 13 grains and legumes, designed to make multigrain chapatis at home. Nutritious and flavorful, it turns every bite into a healthy delight."/>
+    <s v="Horse Gram, Red Gram, Cornflour, Oats, Finger Millet, Soybean, Pearl Millet, Chickpea, Mung Bean, White Sesame Seeds, Urad Dal, Red Chilly Powder, Garlic, Coriander"/>
+    <s v="Add this mix to chakki atta in 1:5 ratio before making the dough, to get the health benefits of 13 grains in every bite."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 146.89kcal, Protein 7.23g, Total Fat 2.84g, Saturated Fat 0.42g, Carbs 23.55g, Fiber 4.57g, Sugars 0.89g, Sodium 0.04g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="360"/>
+    <n v="360"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="21685c21-498d-43b2-88ea-5a64964d64e8"/>
+    <m/>
+    <x v="21"/>
+    <s v="సాంబార్ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Authentic Sambar in a Snap!"/>
+    <s v="A convenient, ready-to-use blend of rice, lentils, spices, and tamarind. Just add vegetables and boil to enjoy a flavorful, authentic South Indian sambar in minutes."/>
+    <s v="Rice, Dry Red Chilly, Coriander, Red Gram, Urad Dal, Chickpea, Tamarind, Salt, Dry Coconut, Cumin, Fenugreek, Cinnamon, Curry Leaf"/>
+    <s v="Add 40g of this authentic blend to 1 liter of water along with your favorite fresh vegetables. Boil until tender for fresh sambar."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 127.92kcal, Protein 5.03g, Total Fat 3.08g, Saturated Fat 1.3g, Carbs 22.92g, Fiber 7.42g, Sugars 2.16g, Sodium 1.13g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="450"/>
+    <n v="450"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="cc119ff6-8f5b-4913-97a1-fb2a95cb2989"/>
+    <m/>
+    <x v="22"/>
+    <s v="పెరి పెరి మసాలా"/>
+    <x v="1"/>
+    <s v="Fiery, Tangy, Totally Irresistible!"/>
+    <s v="A fiery, zesty fusion blend of African bird's eye chilies, garlic, herbs, and spices. Perfect for fries, chips, and snacks."/>
+    <s v="Sugar, Salt, Red Chilly Powder, Onion Powder, Kashmiri Red Chilly Powder, Garlic Powder, Amchur Powder, Black Pepper, Oregano"/>
+    <s v="Dust this zesty chili and herb mix generously over popcorn, makhana, or roasted nuts for a perfectly spicy snack."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.46kcal, Protein 0.32g, Total Fat 0.14g, Saturated Fat 0.04g, Carbs 3.08g, Fiber 0.6g, Sugars 0.92g, Sodium 0.3g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="3"/>
+    <n v="720"/>
+    <n v="720"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="d40333db-fc45-4a73-9329-eb54ef6a85b5"/>
+    <m/>
+    <x v="0"/>
+    <s v="అవిసగింజల కారం"/>
+    <x v="0"/>
+    <s v="Healthy Bite, Enriched with Ragi!"/>
+    <s v="A wholesome podi enriched with flax seeds and finger millet (ragi). Nutty, spicy, and lightly sweet, it delivers nutrition and taste in every bite."/>
+    <s v="Flax Seed, Urad Dal, Peanuts, Finger Millet, Dry Red Chilly, Salt, Garlic, Cloves, Tamarind, Jaggery, Cardamom, Curry Leaf, Cinnamon"/>
+    <s v="Add the desired amount of podi to hot rice. Mix in a spoonful of ghee to enhance the flavor and aroma. Serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.84kcal, Protein 0.85g, Total Fat 1.13g, Saturated Fat 0.14g, Carbs 2.03g, Fiber 1.1g, Sugars 0.21g, Sodium 0.1g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="105"/>
+    <n v="105"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="a72fb41d-834f-4e95-8207-933ee4ce2a47"/>
+    <m/>
+    <x v="1"/>
+    <s v="చింతాకు పొడి"/>
+    <x v="0"/>
+    <s v="Tangy. Nutty. Traditionally Bold!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Peanuts, Black Sesame Seeds, Tamarind Leaves, Dry Red Chilly, Garlic, Coriander, Salt"/>
+    <s v="Add this tangy blend of chinthaku, roasted peanuts, and black sesame to hot rice. Mix in a good serving of ghee and serve warm."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 24.99kcal, Protein 0.96g, Total Fat 1.86g, Saturated Fat 0.3g, Carbs 1.46g, Fiber 0.61g, Sugars 0.13g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="5fd5ad76-ce6b-4a27-b189-bd32180f3c7c"/>
+    <m/>
+    <x v="2"/>
+    <s v="దోశ కారం"/>
+    <x v="0"/>
+    <s v="Perfect Spice for Crispy Dosas!"/>
+    <s v="A flavorful podi crafted for crispy dosas. Made with poha, lentils, and aromatic spices, it adds a nutty, spicy kick that enhances every bite with ghee."/>
+    <s v="Poha, Chickpea, Urad Dal, Coriander, Red Chilly Powder, Dry Red Chilly, Salt, Cumin, Curry Leaf, Garlic, Marathi Moggu, Cinnamon"/>
+    <s v="Evenly dust this vibrant mix of [Ingredient 1] and spices onto your roasting dosa. Finish with a touch of ghee for a spicy, flavorful bite."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.16kcal, Protein 0.67g, Total Fat 0.2g, Saturated Fat 0.02g, Carbs 3.13g, Fiber 0.83g, Sugars 0.17g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="95"/>
+    <n v="95"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="031d0c4a-11ea-49ab-aae9-b7b7d05bd29e"/>
+    <m/>
+    <x v="3"/>
+    <s v="కడప కారం"/>
+    <x v="0"/>
+    <s v="Bold flavor, rich and hearty!"/>
+    <s v="A signature Andhra blend that balances peanuts, garlic, and dry coconut with a fiery kick of red chili. Rich, hearty, and versatile — a true taste of Kadapa tradition."/>
+    <s v="Peanuts, Garlic, Dry Coconut, Cumin, Dry Red Chilly, Coriander, Jaggery, Salt, Red Chilly Powder, Curry Leaf, Lemon Salt"/>
+    <s v="Sprinkle this versatile, sweet-and-spicy blend of peanuts, garlic, and dry coconut over dosas, or mix it into hot rice with ghee. "/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.88kcal, Protein 0.7g, Total Fat 1.49g, Saturated Fat 0.75g, Carbs 1.51g, Fiber 0.64g, Sugars 0.31g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="NEW"/>
+    <s v="ADD"/>
+    <x v="4"/>
+    <s v="కంది పొడి"/>
+    <x v="0"/>
+    <s v="Roasted Lentils,.Pure Comfort!"/>
+    <s v="Traditional Andhra spice powder prepared from sun-dried tamarind leaves, roasted lentils, and dried chilies. Brings a rich, tangy punch to meals."/>
+    <s v="Red Gram, Chickpea, Dry Red Chilly, Coriander, Urad Dal, Garlic, Cumin, Curry Leaf, White Sesame Seeds, Salt, Mung Bean, Fresh Coriander, Red Chilly Powder, Asafoetida"/>
+    <s v="Enjoy the traditional flavor of this multipurpose blend of roasted dals, garlic, and a hint of hing. Mix it into hot rice with a spoonful of ghee, or pair it with your daily tiffins!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 16.02kcal, Protein 0.92g, Total Fat 0.29g, Saturated Fat 0.04g, Carbs 2.71g, Fiber 0.92g, Sugars 0.12g, Sodium 0.08g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="105"/>
+    <n v="105"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="d4eb273f-08a8-4f6b-bfac-8c4dce9c5511"/>
+    <m/>
+    <x v="5"/>
+    <s v="కరివేపాకు పొడి"/>
+    <x v="0"/>
+    <s v="Earthy.Spicy. Naturally Good!"/>
+    <s v="A must-try Andhra specialty made with fragrant curry leaves, dals, and spices. Earthy and wholesome, this podi pairs beautifully with hot rice and ghee for a nourishing meal."/>
+    <s v="Curry Leaf, Garlic, Urad Dal, Dry Red Chilly, Chickpea, Coriander, Tamarind, Salt, Cumin, Fenugreek"/>
+    <s v="Mix the desired amount of this earthy curry leaf, garlic, and tamarind blend into hot rice. Stir in a generous serving of ghee for a comforting, traditional meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.71kcal, Protein 0.81g, Total Fat 0.2g, Saturated Fat 0.05g, Carbs 2.39g, Fiber 1.33g, Sugars 0.23g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="38b67b7f-2441-4024-88f1-f3f0c0a29d00"/>
+    <m/>
+    <x v="6"/>
+    <s v="కర్ణాటక ఇడ్లీ పొడి"/>
+    <x v="0"/>
+    <s v="Idli’s Best Friends: Ghee &amp; Podi!"/>
+    <s v="A classic South Indian podi made with chickpeas, urad dal, and spices. Perfectly balanced for hot idlis with ghee, adding a nutty, mildly spicy flavor every time."/>
+    <s v="Chickpea, Urad Dal, Dry Red Chilly, Salt, Cumin, Black Pepper, Red Chilly Powder, Curry Leaf"/>
+    <s v="Mix this classic blend of roasted dals and black pepper with a generous spoonful of ghee. Spread it right on top for a perfect bite!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.22kcal, Protein 1.03g, Total Fat 0.16g, Saturated Fat 0.02g, Carbs 2.91g, Fiber 1.02g, Sugars 0.32g, Sodium 0.08g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="05dd8c31-48da-4ea0-84bd-345c7c25b5f9"/>
+    <m/>
+    <x v="7"/>
+    <s v="కోనసీమ కారం"/>
+    <x v="0"/>
+    <s v="Superfoods Meet Fiery Tradition!"/>
+    <s v="A signature spice blend inspired by the coastal Konaseema region. Blends dry coconut, garlic, and red chilies for a rich, aromatic flavor."/>
+    <s v="Curry Leaf, Flax Seed, Peanuts, Moringa, Dry Red Chilly, Chickpea, Coriander, Raisin, Fresh Mint, Tamarind, Urad Dal, White Sesame Seeds, Salt, Ginger, Asafoetida"/>
+    <s v="Place Holder"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 15.47kcal, Protein 0.81g, Total Fat 0.71g, Saturated Fat 0.11g, Carbs 1.88g, Fiber 1.1g, Sugars 0.35g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="30"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="125"/>
+    <n v="125"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="7421e0f3-7316-47eb-b75c-c5d92763b9fd"/>
+    <m/>
+    <x v="8"/>
+    <s v="కూర కారం"/>
+    <x v="0"/>
+    <s v="Sauté. Sprinkle. Savor Garlic!"/>
+    <s v="The essential Telugu multi-purpose spice mix used for seasoning daily curries, fries, and gravies. Perfect balance of spices."/>
+    <s v="Dry Coconut, Garlic, Red Chilly Powder, Coriander, Salt"/>
+    <s v="Sauté your everyday vegetables, sprinkle this rich blend of garlic and dry coconut over the top, and savor the bold flavor!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 20.76kcal, Protein 0.39g, Total Fat 1.64g, Saturated Fat 1.37g, Carbs 1.55g, Fiber 0.95g, Sugars 0.23g, Sodium 0.2g"/>
+    <b v="0"/>
+    <b v="0"/>
+    <n v="45"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="98df3516-f8f6-4379-b45e-513b78971171"/>
+    <m/>
+    <x v="9"/>
+    <s v="కొత్తిమీర కారం"/>
+    <x v="0"/>
+    <s v="Zesty coriander Spark – Freshness in Every Spoon!"/>
+    <s v="A vibrant, aromatic spice powder made with fresh sun-dried coriander leaves, roasted dals, and garlic. Earthy and fresh."/>
+    <s v="Red Chilly Powder, Fresh Coriander, Red Gram, Urad Dal, Salt, Poha, Dry Red Chilly, Cumin, Jaggery, Tamarind"/>
+    <s v="Toss this flavorful mix of coriander and roasted dals with hot rice and ghee to bring out the rich, herby aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 12.34kcal, Protein 0.54g, Total Fat 0.23g, Saturated Fat 0.04g, Carbs 2.37g, Fiber 0.77g, Sugars 0.48g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="581f07ae-4d33-4fa1-8915-655e48c183c3"/>
+    <m/>
+    <x v="10"/>
+    <s v="మునగాకు కారం"/>
+    <x v="0"/>
+    <s v="Moringa Magic: Nutritious. Natural. Delicious!"/>
+    <s v="A nutrient-dense South Indian spice blend combining superfood Moringa leaves with roasted lentils and seeds for a savory, earthy flavor. This all-natural &quot;miracle podi&quot; delivers a potent boost of vitamins and antioxidants in every spoonful."/>
+    <s v="Red Gram, Moringa, Chickpea, Pumpkin Seeds, Salt, Dry Red Chilly, Cumin, Black Pepper, Curry Leaf, Mint Leaves, Lemon Salt"/>
+    <s v="Mix the desired amount of this moringa, pumpkin seed blend into hot rice. Stir in a generous serving of ghee for a nutritious meal."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.43kcal, Protein 0.85g, Total Fat 0.39g, Saturated Fat 0.06g, Carbs 1.85g, Fiber 0.62g, Sugars 0.09g, Sodium 0.22g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="115"/>
+    <n v="115"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="ba2fe49f-75f1-4db0-b2d0-edd26d81cc62"/>
+    <m/>
+    <x v="11"/>
+    <s v="నల్ల కారం"/>
+    <x v="0"/>
+    <s v="High fiber, gut-friendly spice!"/>
+    <s v="A wholesome Andhra classic made with tamarind, dals, and garlic. High in fiber and flavor, this podi adds a tangy, spicy twist to everyday favorites."/>
+    <s v="Dry Red Chilly, Chickpea, Urad Dal, Tamarind, Garlic, Coriander, Cumin, Salt, Ghee, Ginger, Jaggery, Curry Leaf"/>
+    <s v="Enjoy this hotel-style blend of roasted dals, fiery chilies, and garlic. Mix it with ghee to dip soft idlis, or sprinkle it over a roasting dosa!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 14.95kcal, Protein 0.63g, Total Fat 0.47g, Saturated Fat 0.15g, Carbs 2.47g, Fiber 0.91g, Sugars 0.52g, Sodium 0.11g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="105"/>
+    <n v="105"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="285b7b12-59d1-47a0-afb2-986c6c72d045"/>
+    <m/>
+    <x v="12"/>
+    <s v="పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Palli Kaaram. Boldly Telugu!"/>
+    <s v="A nutty and spicy Kadapa classic made with peanuts, chili, and curry leaves. A true part of local culture — delicious with rice or even as a snack on its own."/>
+    <s v="Peanuts, Curry Leaf, Dry Red Chilly, Garlic, Red Chilly Powder, Salt, Cumin"/>
+    <s v="Add this unique Rayalaseema blend of roasted peanuts, garlic, and curry leaves to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 25.87kcal, Protein 1.24g, Total Fat 2.04g, Saturated Fat 0.36g, Carbs 1.02g, Fiber 0.64g, Sugars 0.2g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="105"/>
+    <n v="105"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="3d01988a-ad7d-4114-908b-38098cd63bd3"/>
+    <m/>
+    <x v="13"/>
+    <s v="పుదిన కారం"/>
+    <x v="0"/>
+    <s v="Light, Lively &amp; Minty-Perfect!"/>
+    <s v="A refreshing and aromatic South Indian spice blend featuring sun-dried mint, garlic, and roasted lentils for a zesty, herbaceous kick. This flavorful podi acts as a natural palate cleanser while providing a cooling, gut-friendly boost to your daily meals."/>
+    <s v="Red Chilly Powder, Mint Leaves, Urad Dal, Red Gram, Poha, Salt, Dry Red Chilly, Cumin, Tamarind, Jaggery"/>
+    <s v="Add this refreshing blend of mint leaves, roasted dals, and a hint of tamarind to hot rice. Mix in a spoonful of ghee and serve warm!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.89kcal, Protein 0.65g, Total Fat 0.26g, Saturated Fat 0.05g, Carbs 2.65g, Fiber 0.95g, Sugars 0.47g, Sodium 0.26g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="5d7272ee-37e6-43c3-bb9d-551dc2d7da38"/>
+    <m/>
+    <x v="14"/>
+    <s v=" పుట్నాల పొడి"/>
+    <x v="0"/>
+    <s v="Flavor-packed, protein-rich!"/>
+    <s v="A protein-rich lentil blend from Kadapa, this podi combines fried gram, coconut, and garlic for a nutty, savory taste. Traditionally enjoyed with pickle rice and ghee for an extra flavor boost."/>
+    <s v="Fried Gram, Dry Coconut, Garlic, Red Chilly Powder, Salt"/>
+    <s v="Add this classic blend of fried gram, dry coconut, and garlic to hot rice. Mix in a spoonful of ghee and pair with your favorite pickle for a perfect meal!"/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 18kcal, Protein 0.9g, Total Fat 0.55g, Saturated Fat 0.31g, Carbs 2.53g, Fiber 0.6g, Sugars 0.45g, Sodium 0.06g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="2cf104b5-c88f-48a7-9e5e-741a20cc2c20"/>
+    <m/>
+    <x v="15"/>
+    <s v="స్పెషల్ గోధుమ కారం"/>
+    <x v="0"/>
+    <s v="Tasty, Light &amp; Fresh!"/>
+    <s v="A wholesome, nutty podi made with chakki atta, dals, coconut, and garlic. Perfectly balanced, it brings a bold, hearty flavor to your meals."/>
+    <s v="Chakki Atta, Urad Dal, Red Chilly Powder, Dry Coconut, Flax Seed, Garlic, Salt"/>
+    <s v="Smear this unique, nutty mix of whole wheat, urad dal, and garlic onto dosas, or pair it with melted ghee for the perfect savory idli dip."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 17.24kcal, Protein 0.68g, Total Fat 0.41g, Saturated Fat 0.2g, Carbs 2.93g, Fiber 0.76g, Sugars 0.09g, Sodium 0.07g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="95"/>
+    <n v="95"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="0219fa3e-9afc-4048-aba2-e9daa0fba81e"/>
+    <m/>
+    <x v="16"/>
+    <s v=" స్పెషల్ పల్లి కారం"/>
+    <x v="0"/>
+    <s v="Rustic. Rich. Ridiculously Good!"/>
+    <s v="Our best-reviewed podi! A rustic blend of peanuts, coriander, and jaggery that delivers mellow, nutty flavors. Smooth and balanced, it’s even loved by kids when mixed with hot rice and ghee."/>
+    <s v="Peanuts, Fried Gram, Coriander, Jaggery, Dry Red Chilly, Salt, Tamarind"/>
+    <s v="Toss this flavorful mix of peanuts, fried gram, and coriander with hot rice and a good serving of ghee to beautifully bring out the sweet and tangy notes."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 19.99kcal, Protein 0.87g, Total Fat 1.03g, Saturated Fat 0.16g, Carbs 2.23g, Fiber 0.69g, Sugars 0.85g, Sodium 0.13g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="976a762d-59d8-421e-8a1a-dc0bd38850ea"/>
+    <m/>
+    <x v="17"/>
+    <s v="తమలపాకు కారం"/>
+    <x v="0"/>
+    <s v="Wellness in Every Bite – Betel Leaf at the Heart!"/>
+    <s v="A unique, health-focused herbal spice powder combining fresh betel leaves (Tamalapaaku) with traditional roasted spices and lentils."/>
+    <s v="Betel Leaf, Garlic, Urad Dal, Chickpea, Peanuts, Red Chilly Powder, Cumin, White Sesame Seeds, Coriander, Salt, Curry Leaf"/>
+    <s v="Stir this vibrantly fresh betel leaf and sesame mix into hot rice with a spoonful of ghee for an uplifting flavor."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.23kcal, Protein 0.66g, Total Fat 0.57g, Saturated Fat 0.09g, Carbs 1.64g, Fiber 0.65g, Sugars 0.16g, Sodium 0.09g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="140"/>
+    <n v="140"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="6bb57327-d5c7-4a3f-b645-031fe220a609"/>
+    <m/>
+    <x v="18"/>
+    <s v="వెల్లుల్లి కారం"/>
+    <x v="0"/>
+    <s v="Three Ingredients. Infinite Flavor!"/>
+    <s v="A garlicky podi with dry coconut and spices, a staple in every Kadapa household. Adds delicious flavor to sautéed vegetables or can be used as a base for curries."/>
+    <s v="Garlic, Red Chilly Powder, Salt, Sunflower Oil"/>
+    <s v="Smear this savory garlic blend onto hot dosas, or toss it with hot rice and ghee to bring out the roasted aroma."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 10.59kcal, Protein 0.42g, Total Fat 0.45g, Saturated Fat 0.07g, Carbs 1.77g, Fiber 0.75g, Sugars 0.17g, Sodium 0.25g"/>
+    <b v="1"/>
+    <b v="1"/>
+    <n v="60"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="110"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="81095baa-0101-4c50-8749-051c376d8fd8"/>
+    <m/>
+    <x v="19"/>
+    <s v="చట్నీ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Fresh Chutney in a Snap!"/>
+    <s v="A quick and easy blend of peanuts, gram, and spices. Just add water and grind to make a smooth, flavorful Palli (groundnut) chutney in minutes."/>
+    <s v="Peanuts, Fried Gram, Dry Red Chilly, Salt, Ginger, Tamarind, Coriander Powder"/>
+    <s v="Simply add water gradually to this flavorful blend until you reach your desired consistency.Ready in seconds to pair with hot tiffin."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 178.61kcal, Protein 9.01g, Total Fat 10.89g, Saturated Fat 1.83g, Carbs 13.74g, Fiber 5.08g, Sugars 2.74g, Sodium 0.64g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="95"/>
+    <n v="95"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="9b6b3df2-7a39-407f-b320-9d6f6e9b0db9"/>
+    <m/>
+    <x v="20"/>
+    <s v="మల్టీ గ్రెయిన్ మిక్స్"/>
+    <x v="1"/>
+    <s v="Power of 13 Grains, Strength in Every Bite!"/>
+    <s v="A wholesome blend of 13 grains and legumes, designed to make multigrain chapatis at home. Nutritious and flavorful, it turns every bite into a healthy delight."/>
+    <s v="Horse Gram, Red Gram, Cornflour, Oats, Finger Millet, Soybean, Pearl Millet, Chickpea, Mung Bean, White Sesame Seeds, Urad Dal, Red Chilly Powder, Garlic, Coriander"/>
+    <s v="Add this mix to chakki atta in 1:5 ratio before making the dough, to get the health benefits of 13 grains in every bite."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 146.89kcal, Protein 7.23g, Total Fat 2.84g, Saturated Fat 0.42g, Carbs 23.55g, Fiber 4.57g, Sugars 0.89g, Sodium 0.04g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="90"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="90"/>
+    <n v="90"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="21685c21-498d-43b2-88ea-5a64964d64e8"/>
+    <m/>
+    <x v="21"/>
+    <s v="సాంబార్ ప్రీమిక్స్"/>
+    <x v="1"/>
+    <s v="Authentic Sambar in a Snap!"/>
+    <s v="A convenient, ready-to-use blend of rice, lentils, spices, and tamarind. Just add vegetables and boil to enjoy a flavorful, authentic South Indian sambar in minutes."/>
+    <s v="Rice, Dry Red Chilly, Coriander, Red Gram, Urad Dal, Chickpea, Tamarind, Salt, Dry Coconut, Cumin, Fenugreek, Cinnamon, Curry Leaf"/>
+    <s v="Add 40g of this authentic blend to 1 liter of water along with your favorite fresh vegetables. Boil until tender for fresh sambar."/>
+    <n v="40"/>
+    <s v="Serving Size 40g, Total Servings 20, Calories 127.92kcal, Protein 5.03g, Total Fat 3.08g, Saturated Fat 1.3g, Carbs 22.92g, Fiber 7.42g, Sugars 2.16g, Sodium 1.13g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="100"/>
+    <n v="100"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="cc119ff6-8f5b-4913-97a1-fb2a95cb2989"/>
+    <s v="oca"/>
+    <x v="22"/>
+    <s v="పెరి పెరి మసాలా"/>
+    <x v="1"/>
+    <s v="Fiery, Tangy, Totally Irresistible!"/>
+    <s v="A fiery, zesty fusion blend of African bird's eye chilies, garlic, herbs, and spices. Perfect for fries, chips, and snacks."/>
+    <s v="Sugar, Salt, Red Chilly Powder, Onion Powder, Kashmiri Red Chilly Powder, Garlic Powder, Amchur Powder, Black Pepper, Oregano"/>
+    <s v="Dust this zesty chili and herb mix generously over popcorn, makhana, or roasted nuts for a perfectly spicy snack."/>
+    <n v="5"/>
+    <s v="Serving Size 5g, Total Servings 20, Calories 13.46kcal, Protein 0.32g, Total Fat 0.14g, Saturated Fat 0.04g, Carbs 3.08g, Fiber 0.6g, Sugars 0.92g, Sodium 0.3g"/>
+    <b v="0"/>
+    <b v="1"/>
+    <n v="120"/>
+    <b v="0"/>
+    <x v="0"/>
+    <n v="130"/>
+    <n v="130"/>
+    <n v="100"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="31b0afc4-646a-4ad9-91b7-4a6686e6057c"/>
+    <m/>
+    <x v="23"/>
+    <s v="రాగి చపాతీ"/>
+    <x v="2"/>
+    <s v="Wholesome Ragi. Fresh Chakki Goodness!"/>
+    <s v="Healthy, soft chapatis prepared from a nutritious blend of finger millet (Ragi) flour and whole wheat. Ready to cook on the tawa."/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Carbs: , Fiber: , Sodium: , Sugars: , Protein: , Calories: , Total_fat: , Saturated_fat: , Total_servings: 20"/>
+    <b v="0"/>
+    <b v="0"/>
+    <m/>
+    <b v="1"/>
+    <x v="4"/>
+    <n v="70"/>
+    <n v="70"/>
+    <n v="100"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="68b1f314-d303-4429-bb42-d4c7cbbd9bec"/>
+    <m/>
+    <x v="24"/>
+    <s v="మలబార్ పరోటా"/>
+    <x v="2"/>
+    <s v="Flaky. Buttery. Irresistibly South Indian!"/>
+    <s v="Traditional flaky layered Malabar parottas made with premium ingredients, delivering authentic Kerala street-food taste at home."/>
+    <s v="All-Purpose Flour, Sunflower Oil, Vanaspati, Water, Salt"/>
+    <s v="Remove the parotta from the pack and heat on a preheated tawa for 30–40 seconds on each side. Store in the refrigerator."/>
+    <s v="1pcs"/>
+    <s v="Carbs: 37.25g, Fiber: 1.32g, Sodium: 0.19g, Sugars: 0.13g, Protein: 5.03g, Calories: 211.73kcal, Total_fat: 4.16g, Saturated_fat: 0.89g, Total_servings: 20"/>
+    <b v="0"/>
+    <b v="1"/>
+    <m/>
+    <b v="1"/>
+    <x v="4"/>
+    <n v="155"/>
+    <n v="155"/>
+    <n v="994"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="b35aedcb-b9e5-43e4-a8bd-4fbe1b340fb6"/>
+    <m/>
+    <x v="25"/>
+    <s v="వీట్ పరోటా"/>
+    <x v="2"/>
+    <s v="Whole Grain Power. Guilt-Free Indulgence!"/>
+    <s v="Healthy whole wheat parottas with rich layers and hearty flavour, combining nutrition and indulgent South Indian taste."/>
+    <s v="Whole Wheat Atta, Sunflower Oil, Vanaspati, Water, Salt"/>
+    <s v="Remove the parotta from the pack and heat on a preheated tawa for 30–40 seconds on each side. Store in the refrigerator."/>
+    <s v="1pcs"/>
+    <s v="Carbs: 35.36g, Fiber: 5.26g, Sodium: 0.98g, Sugars: 0.2g, Protein: 6.48g, Calories: 201.24kcal, Total_fat: 4.79g, Saturated_fat: 1.03g, Total_servings: 20, Additional_info: 0.25gms Trans Fat per serving."/>
+    <b v="1"/>
+    <b v="1"/>
+    <m/>
+    <b v="1"/>
+    <x v="4"/>
+    <n v="165"/>
+    <n v="165"/>
+    <n v="96"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="1b53eba0-1a68-4e3b-80bf-e585ca8e0cdb"/>
+    <m/>
+    <x v="26"/>
+    <s v="పూరి"/>
+    <x v="2"/>
+    <s v="Wholesome Puri! Full Chakki Atta  freshness!"/>
+    <s v="Golden, fluffy puris made from 100% whole wheat chakki atta. These ready-to-fry delights offer a light, airy texture and authentic home-style taste, perfect for festive meals or weekend breakfasts."/>
+    <s v="Poori Atta, Chakki Atta, Samolina, Water, Salt, Sunflower Oil"/>
+    <m/>
+    <s v="1pcs"/>
+    <s v="Carbs: 21.72g, Fiber: 3.46g, Sodium: 0.11g, Sugars: 0.12g, Protein: 3.87g, Calories: 108.33kcal, Total_fat: 1.22g, Saturated_fat: 0.18g, Total_servings: 20"/>
+    <b v="0"/>
+    <b v="1"/>
+    <m/>
+    <b v="1"/>
+    <x v="4"/>
+    <n v="65"/>
+    <n v="65"/>
+    <n v="99"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="f3675b00-7f3c-4222-b5c8-58576f22394b"/>
+    <m/>
+    <x v="27"/>
+    <s v="గోధుమ చపాతీ"/>
+    <x v="2"/>
+    <s v="Soft Rotis. Pure Home Taste!"/>
+    <s v="Soft, wholesome wheat chapathi made from carefully selected wheat flour. Perfect balance of nutrition and taste, ideal for wrapping curries or enjoying with dal and vegetables."/>
+    <s v="Chakki Atta, Water, Salt, Sunflower Oil"/>
+    <s v="Remove the chapathi from the pack and heat on a preheated tawa for 20–30 seconds on each side. Store in the refrigerator."/>
+    <s v="1pcs"/>
+    <s v="Carbs: 16.55g, Fiber: 2.46g, Sodium: 0.09g, Sugars: 0.09g, Protein: 3.03g, Calories: 88.32kcal, Total_fat: 1.58g, Saturated_fat: 0.22g, Total_servings: 20, Additional_info: "/>
+    <b v="0"/>
+    <b v="1"/>
+    <m/>
+    <b v="1"/>
+    <x v="4"/>
+    <n v="85"/>
+    <n v="85"/>
+    <n v="996"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="615824c3-500f-4bcc-9ce3-30e49672dc21"/>
+    <m/>
+    <x v="28"/>
+    <s v="మలబార్ పరోటా"/>
+    <x v="2"/>
+    <s v="Flaky. Buttery. Irresistibly South Indian!"/>
+    <s v="Traditional flaky layered Malabar parottas made with premium ingredients, delivering authentic Kerala street-food taste at home."/>
+    <s v="All-Purpose Flour, Sunflower Oil, Vanaspati, Water, Salt"/>
+    <s v="Remove the parotta from the pack and heat on a preheated tawa for 30–40 seconds on each side. Store in the refrigerator."/>
+    <s v="1pcs"/>
+    <s v="Carbs: 35.36g, Fiber: 5.26g, Sodium: 0.98g, Sugars: 0.2g, Protein: 6.48g, Calories: 201.24kcal, Total_fat: 4.79g, Saturated_fat: 1.03g, Total_servings: 20"/>
+    <b v="0"/>
+    <b v="1"/>
+    <m/>
+    <b v="1"/>
+    <x v="5"/>
+    <n v="85"/>
+    <n v="85"/>
+    <n v="800"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CCE3CC62-2BA3-439F-8658-4D1EDF0C450D}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:I38" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="30">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="10"/>
+        <item x="20"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="27"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item m="1" x="6"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="4"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="33">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="19"/>
+    <field x="15"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of variant_mrp" fld="16" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="0">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="19" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="15" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="19" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="15" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+          <reference field="19" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="15" count="2">
+            <x v="1"/>
+            <x v="3"/>
+          </reference>
+          <reference field="19" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1204,7 +4645,845 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C6C8CE-8C03-4151-968F-0DF3EDE78890}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A3:I38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
+        <v>155</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5">
+        <v>85</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5">
+        <v>65</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
+        <v>70</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5">
+        <v>85</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
+        <v>165</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5">
+        <v>105</v>
+      </c>
+      <c r="C14" s="5">
+        <v>495</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5">
+        <v>255</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <v>55</v>
+      </c>
+      <c r="H14" s="5">
+        <v>135</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5">
+        <v>120</v>
+      </c>
+      <c r="C15" s="5">
+        <v>630</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5">
+        <v>325</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
+        <v>70</v>
+      </c>
+      <c r="H15" s="5">
+        <v>170</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="5">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5">
+        <v>405</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5">
+        <v>210</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5">
+        <v>45</v>
+      </c>
+      <c r="H16" s="5">
+        <v>110</v>
+      </c>
+      <c r="I16" s="5">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="5">
+        <v>110</v>
+      </c>
+      <c r="C17" s="5">
+        <v>540</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5">
+        <v>280</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5">
+        <v>60</v>
+      </c>
+      <c r="H17" s="5">
+        <v>145</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="5">
+        <v>105</v>
+      </c>
+      <c r="C18" s="5">
+        <v>495</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5">
+        <v>255</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5">
+        <v>55</v>
+      </c>
+      <c r="H18" s="5">
+        <v>135</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="5">
+        <v>110</v>
+      </c>
+      <c r="C19" s="5">
+        <v>540</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5">
+        <v>280</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5">
+        <v>60</v>
+      </c>
+      <c r="H19" s="5">
+        <v>145</v>
+      </c>
+      <c r="I19" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5">
+        <v>100</v>
+      </c>
+      <c r="C20" s="5">
+        <v>450</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5">
+        <v>230</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5">
+        <v>50</v>
+      </c>
+      <c r="H20" s="5">
+        <v>120</v>
+      </c>
+      <c r="I20" s="5">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5">
+        <v>125</v>
+      </c>
+      <c r="C21" s="5">
+        <v>675</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5">
+        <v>350</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
+        <v>75</v>
+      </c>
+      <c r="H21" s="5">
+        <v>180</v>
+      </c>
+      <c r="I21" s="5">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="5">
+        <v>110</v>
+      </c>
+      <c r="C22" s="5">
+        <v>540</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5">
+        <v>280</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
+        <v>60</v>
+      </c>
+      <c r="H22" s="5">
+        <v>145</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="5">
+        <v>110</v>
+      </c>
+      <c r="C23" s="5">
+        <v>540</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5">
+        <v>280</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
+        <v>60</v>
+      </c>
+      <c r="H23" s="5">
+        <v>145</v>
+      </c>
+      <c r="I23" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="5">
+        <v>115</v>
+      </c>
+      <c r="C24" s="5">
+        <v>585</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5">
+        <v>300</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
+        <v>65</v>
+      </c>
+      <c r="H24" s="5">
+        <v>160</v>
+      </c>
+      <c r="I24" s="5">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="5">
+        <v>105</v>
+      </c>
+      <c r="C25" s="5">
+        <v>495</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5">
+        <v>255</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5">
+        <v>55</v>
+      </c>
+      <c r="H25" s="5">
+        <v>135</v>
+      </c>
+      <c r="I25" s="5">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5">
+        <v>105</v>
+      </c>
+      <c r="C26" s="5">
+        <v>495</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5">
+        <v>255</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5">
+        <v>55</v>
+      </c>
+      <c r="H26" s="5">
+        <v>135</v>
+      </c>
+      <c r="I26" s="5">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5">
+        <v>110</v>
+      </c>
+      <c r="C27" s="5">
+        <v>540</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5">
+        <v>280</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5">
+        <v>60</v>
+      </c>
+      <c r="H27" s="5">
+        <v>145</v>
+      </c>
+      <c r="I27" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5">
+        <v>100</v>
+      </c>
+      <c r="C28" s="5">
+        <v>450</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5">
+        <v>230</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5">
+        <v>50</v>
+      </c>
+      <c r="H28" s="5">
+        <v>120</v>
+      </c>
+      <c r="I28" s="5">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5">
+        <v>95</v>
+      </c>
+      <c r="C29" s="5">
+        <v>405</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5">
+        <v>210</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5">
+        <v>45</v>
+      </c>
+      <c r="H29" s="5">
+        <v>110</v>
+      </c>
+      <c r="I29" s="5">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5">
+        <v>110</v>
+      </c>
+      <c r="C30" s="5">
+        <v>540</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5">
+        <v>280</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5">
+        <v>60</v>
+      </c>
+      <c r="H30" s="5">
+        <v>145</v>
+      </c>
+      <c r="I30" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5">
+        <v>140</v>
+      </c>
+      <c r="C31" s="5">
+        <v>810</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5">
+        <v>420</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5">
+        <v>90</v>
+      </c>
+      <c r="H31" s="5">
+        <v>220</v>
+      </c>
+      <c r="I31" s="5">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5">
+        <v>110</v>
+      </c>
+      <c r="C32" s="5">
+        <v>540</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5">
+        <v>280</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5">
+        <v>60</v>
+      </c>
+      <c r="H32" s="5">
+        <v>145</v>
+      </c>
+      <c r="I32" s="5">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5">
+        <v>95</v>
+      </c>
+      <c r="C34" s="5">
+        <v>405</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5">
+        <v>210</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5">
+        <v>45</v>
+      </c>
+      <c r="H34" s="5">
+        <v>110</v>
+      </c>
+      <c r="I34" s="5">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5">
+        <v>90</v>
+      </c>
+      <c r="C35" s="5">
+        <v>360</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5">
+        <v>185</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5">
+        <v>40</v>
+      </c>
+      <c r="H35" s="5">
+        <v>95</v>
+      </c>
+      <c r="I35" s="5">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="5">
+        <v>130</v>
+      </c>
+      <c r="C36" s="5">
+        <v>720</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5">
+        <v>370</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5">
+        <v>80</v>
+      </c>
+      <c r="H36" s="5">
+        <v>195</v>
+      </c>
+      <c r="I36" s="5">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="5">
+        <v>100</v>
+      </c>
+      <c r="C37" s="5">
+        <v>450</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5">
+        <v>230</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5">
+        <v>50</v>
+      </c>
+      <c r="H37" s="5">
+        <v>120</v>
+      </c>
+      <c r="I37" s="5">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2495</v>
+      </c>
+      <c r="C38" s="5">
+        <v>12105</v>
+      </c>
+      <c r="D38" s="5">
+        <v>540</v>
+      </c>
+      <c r="E38" s="5">
+        <v>6250</v>
+      </c>
+      <c r="F38" s="5">
+        <v>85</v>
+      </c>
+      <c r="G38" s="5">
+        <v>1345</v>
+      </c>
+      <c r="H38" s="5">
+        <v>3265</v>
+      </c>
+      <c r="I38" s="5">
+        <v>26085</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="7.874015748031496E-2" right="7.874015748031496E-2" top="7.874015748031496E-2" bottom="7.874015748031496E-2" header="7.874015748031496E-2" footer="7.874015748031496E-2"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68C05BD-1FB5-4FE3-A452-4C15B491BDE4}">
+  <sheetPr codeName="Sheet2" filterMode="1"/>
   <dimension ref="A1:T122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1292,9 +5571,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -1352,9 +5631,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -1412,9 +5691,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
@@ -1472,9 +5751,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
@@ -1532,7 +5811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -1594,9 +5873,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
@@ -1654,9 +5933,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
@@ -1714,9 +5993,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
@@ -1774,9 +6053,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
@@ -1834,9 +6113,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
@@ -1894,9 +6173,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
@@ -1954,9 +6233,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
@@ -2014,9 +6293,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -2074,9 +6353,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -2134,9 +6413,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -2194,9 +6473,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="2" t="s">
@@ -2254,9 +6533,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="2" t="s">
@@ -2314,9 +6593,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="2" t="s">
@@ -2374,9 +6653,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="19.5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
@@ -2436,7 +6715,7 @@
     </row>
     <row r="21" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
@@ -2446,7 +6725,7 @@
         <v>162</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>163</v>
@@ -2496,7 +6775,7 @@
     </row>
     <row r="22" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="2" t="s">
@@ -2506,7 +6785,7 @@
         <v>168</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>169</v>
@@ -2556,7 +6835,7 @@
     </row>
     <row r="23" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="2" t="s">
@@ -2566,7 +6845,7 @@
         <v>174</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>175</v>
@@ -2616,7 +6895,7 @@
     </row>
     <row r="24" spans="1:20" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="2" t="s">
@@ -2626,7 +6905,7 @@
         <v>180</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>181</v>
@@ -2674,9 +6953,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -2734,9 +7013,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -2794,9 +7073,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -2854,9 +7133,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -2914,7 +7193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -2976,9 +7255,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -3036,9 +7315,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -3096,9 +7375,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
@@ -3156,9 +7435,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
@@ -3216,9 +7495,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -3276,9 +7555,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -3336,9 +7615,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -3396,9 +7675,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -3456,9 +7735,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -3516,9 +7795,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -3576,9 +7855,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -3636,9 +7915,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -3696,9 +7975,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -3756,9 +8035,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -3818,7 +8097,7 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -3828,7 +8107,7 @@
         <v>162</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>163</v>
@@ -3878,7 +8157,7 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -3888,7 +8167,7 @@
         <v>168</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>169</v>
@@ -3938,7 +8217,7 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -3948,7 +8227,7 @@
         <v>174</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>175</v>
@@ -3998,7 +8277,7 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1" t="s">
@@ -4008,7 +8287,7 @@
         <v>180</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>181</v>
@@ -4056,9 +8335,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
@@ -4116,9 +8395,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
@@ -4176,9 +8455,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
@@ -4236,9 +8515,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
@@ -4296,7 +8575,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>27</v>
       </c>
@@ -4358,9 +8637,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
@@ -4418,9 +8697,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
@@ -4478,9 +8757,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
@@ -4538,9 +8817,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
@@ -4598,9 +8877,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
@@ -4658,9 +8937,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
@@ -4718,9 +8997,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
@@ -4778,9 +9057,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
@@ -4838,9 +9117,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
@@ -4898,9 +9177,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1" t="s">
@@ -4958,9 +9237,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
@@ -5018,9 +9297,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="1" t="s">
@@ -5078,9 +9357,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
@@ -5138,9 +9417,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
@@ -5200,7 +9479,7 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
@@ -5210,7 +9489,7 @@
         <v>162</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>163</v>
@@ -5260,7 +9539,7 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
@@ -5270,7 +9549,7 @@
         <v>168</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>169</v>
@@ -5320,7 +9599,7 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
@@ -5330,7 +9609,7 @@
         <v>174</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>175</v>
@@ -5380,7 +9659,7 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
@@ -5390,7 +9669,7 @@
         <v>180</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>181</v>
@@ -5438,9 +9717,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
@@ -5498,9 +9777,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
@@ -5558,9 +9837,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
@@ -5618,9 +9897,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
@@ -5678,7 +9957,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>27</v>
       </c>
@@ -5740,9 +10019,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
@@ -5800,9 +10079,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="1" t="s">
@@ -5860,9 +10139,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1" t="s">
@@ -5920,9 +10199,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1" t="s">
@@ -5980,9 +10259,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
@@ -6040,9 +10319,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
@@ -6100,9 +10379,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
@@ -6160,9 +10439,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
@@ -6220,9 +10499,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
@@ -6280,9 +10559,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
@@ -6340,9 +10619,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
@@ -6400,9 +10679,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
@@ -6460,9 +10739,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
@@ -6520,9 +10799,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
@@ -6582,7 +10861,7 @@
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
@@ -6592,7 +10871,7 @@
         <v>162</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>163</v>
@@ -6642,7 +10921,7 @@
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
@@ -6652,7 +10931,7 @@
         <v>168</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>169</v>
@@ -6702,7 +10981,7 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B92" s="1"/>
       <c r="C92" s="1" t="s">
@@ -6712,7 +10991,7 @@
         <v>174</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>175</v>
@@ -6762,7 +11041,7 @@
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
@@ -6772,7 +11051,7 @@
         <v>180</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>181</v>
@@ -6820,9 +11099,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
@@ -6880,9 +11159,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -6940,9 +11219,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
@@ -7000,9 +11279,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
@@ -7060,7 +11339,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>27</v>
       </c>
@@ -7122,9 +11401,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
@@ -7182,9 +11461,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
@@ -7242,9 +11521,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
@@ -7302,9 +11581,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
@@ -7362,9 +11641,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
@@ -7422,9 +11701,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
@@ -7482,9 +11761,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
@@ -7542,9 +11821,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
@@ -7602,9 +11881,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
@@ -7662,9 +11941,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
@@ -7722,9 +12001,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
@@ -7782,9 +12061,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
@@ -7842,9 +12121,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
@@ -7902,9 +12181,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
@@ -7964,7 +12243,7 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
@@ -7974,7 +12253,7 @@
         <v>162</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>163</v>
@@ -8024,7 +12303,7 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
@@ -8034,7 +12313,7 @@
         <v>168</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>169</v>
@@ -8084,7 +12363,7 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
@@ -8094,7 +12373,7 @@
         <v>174</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>175</v>
@@ -8144,7 +12423,7 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>190</v>
@@ -8156,7 +12435,7 @@
         <v>180</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>181</v>
@@ -8204,7 +12483,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>191</v>
       </c>
@@ -8218,7 +12497,7 @@
         <v>194</v>
       </c>
       <c r="F117" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G117" t="s">
         <v>195</v>
@@ -8236,7 +12515,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="Q117">
         <v>70</v>
@@ -8251,48 +12530,48 @@
         <v>187</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>197</v>
+      </c>
+      <c r="C118" t="s">
         <v>198</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>199</v>
-      </c>
-      <c r="D118" t="s">
-        <v>200</v>
       </c>
       <c r="E118" t="s">
         <v>194</v>
       </c>
       <c r="F118" t="s">
+        <v>200</v>
+      </c>
+      <c r="G118" t="s">
         <v>201</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>202</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>203</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>204</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>205</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" t="b">
+        <v>1</v>
+      </c>
+      <c r="P118" t="s">
         <v>206</v>
-      </c>
-      <c r="L118" t="b">
-        <v>0</v>
-      </c>
-      <c r="M118" t="b">
-        <v>1</v>
-      </c>
-      <c r="O118" t="b">
-        <v>1</v>
-      </c>
-      <c r="P118" t="s">
-        <v>207</v>
       </c>
       <c r="Q118">
         <v>155</v>
@@ -8307,37 +12586,37 @@
         <v>187</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>207</v>
+      </c>
+      <c r="C119" t="s">
         <v>208</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>209</v>
-      </c>
-      <c r="D119" t="s">
-        <v>210</v>
       </c>
       <c r="E119" t="s">
         <v>194</v>
       </c>
       <c r="F119" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G119" t="s">
+        <v>210</v>
+      </c>
+      <c r="H119" t="s">
         <v>211</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
+        <v>203</v>
+      </c>
+      <c r="J119" t="s">
+        <v>204</v>
+      </c>
+      <c r="K119" t="s">
         <v>212</v>
       </c>
-      <c r="I119" t="s">
-        <v>204</v>
-      </c>
-      <c r="J119" t="s">
-        <v>205</v>
-      </c>
-      <c r="K119" t="s">
-        <v>213</v>
-      </c>
       <c r="L119" t="b">
         <v>1</v>
       </c>
@@ -8348,7 +12627,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q119">
         <v>165</v>
@@ -8363,34 +12642,34 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>213</v>
+      </c>
+      <c r="C120" t="s">
         <v>214</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>215</v>
-      </c>
-      <c r="D120" t="s">
-        <v>216</v>
       </c>
       <c r="E120" t="s">
         <v>194</v>
       </c>
       <c r="F120" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G120" t="s">
+        <v>216</v>
+      </c>
+      <c r="H120" t="s">
         <v>217</v>
       </c>
-      <c r="H120" t="s">
+      <c r="J120" t="s">
+        <v>204</v>
+      </c>
+      <c r="K120" t="s">
         <v>218</v>
       </c>
-      <c r="J120" t="s">
-        <v>205</v>
-      </c>
-      <c r="K120" t="s">
-        <v>219</v>
-      </c>
       <c r="L120" t="b">
         <v>0</v>
       </c>
@@ -8401,7 +12680,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q120">
         <v>65</v>
@@ -8416,37 +12695,37 @@
         <v>187</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>219</v>
+      </c>
+      <c r="C121" t="s">
         <v>220</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>221</v>
-      </c>
-      <c r="D121" t="s">
-        <v>222</v>
       </c>
       <c r="E121" t="s">
         <v>194</v>
       </c>
       <c r="F121" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G121" t="s">
+        <v>222</v>
+      </c>
+      <c r="H121" t="s">
         <v>223</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
         <v>224</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
+        <v>204</v>
+      </c>
+      <c r="K121" t="s">
         <v>225</v>
       </c>
-      <c r="J121" t="s">
-        <v>205</v>
-      </c>
-      <c r="K121" t="s">
-        <v>226</v>
-      </c>
       <c r="L121" t="b">
         <v>0</v>
       </c>
@@ -8457,7 +12736,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q121">
         <v>85</v>
@@ -8472,48 +12751,48 @@
         <v>187</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" t="s">
         <v>227</v>
       </c>
-      <c r="C122" t="s">
-        <v>228</v>
-      </c>
       <c r="D122" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E122" t="s">
         <v>194</v>
       </c>
       <c r="F122" t="s">
+        <v>200</v>
+      </c>
+      <c r="G122" t="s">
         <v>201</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>202</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
         <v>203</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>204</v>
       </c>
-      <c r="J122" t="s">
-        <v>205</v>
-      </c>
       <c r="K122" t="s">
+        <v>228</v>
+      </c>
+      <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="b">
+        <v>1</v>
+      </c>
+      <c r="O122" t="b">
+        <v>1</v>
+      </c>
+      <c r="P122" t="s">
         <v>229</v>
-      </c>
-      <c r="L122" t="b">
-        <v>0</v>
-      </c>
-      <c r="M122" t="b">
-        <v>1</v>
-      </c>
-      <c r="O122" t="b">
-        <v>1</v>
-      </c>
-      <c r="P122" t="s">
-        <v>230</v>
       </c>
       <c r="Q122">
         <v>85</v>
@@ -8529,6 +12808,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T122" xr:uid="{A68C05BD-1FB5-4FE3-A452-4C15B491BDE4}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Chutney Premix"/>
+        <filter val="MultiGrain Mix"/>
+        <filter val="Peri Peri Masala"/>
+        <filter val="Sambar Premix"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>